--- a/docs/architecture/v0-compliance-matrix.xlsx
+++ b/docs/architecture/v0-compliance-matrix.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High-risk findings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matrix'!$A$1:$I$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matrix'!$A$1:$I$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +37,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -62,11 +62,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4B084"/>
       </patternFill>
     </fill>
     <fill>
@@ -101,9 +96,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,9 +114,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -493,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -854,32 +846,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>RBAC (6 system roles + custom roles, `@RequirePermissions`) tested by a 6-role × 22-capability matrix (tests/api/permissions.test.ts, 147 tests). Company level = scope ALL|ASSIGNED only (company_assignment).</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>packages/contracts/src/authz.ts (pure rules), apps/api/src/common/access.ts (AccessContext), org.guard.ts; tables organisation_membership / practice_membership / company_membership; tests: packages/contracts/src/authz.test.ts (22), tests/api/hierarchy.test.ts (25), tests/db/hierarchy.test.ts (16), tests/api/permissions.test.ts (matrix for 8 system roles x 26 probes), tests/unit/architecture.test.ts (central-authoriser rules)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Medium — a user cannot hold different roles/permissions per company (e.g. Accountant on A, Viewer on B). Practices commonly need this.</t>
+          <t>Low - none</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Decide: add per-company role override (company_assignment.role_id) or accept scope-only; document in ADR</t>
+          <t>None (UI for managing grants is Tranche B)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>tests/api/tenancy.test.ts (assigned scope); add per-company role tests if adopted</t>
+          <t>pnpm test (hierarchy, authz, permissions suites)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1551,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CI run #7 (sha e06fbd7) all 8 jobs green; local: 459 unit/integration, 4 e2e, 29 infra (+2 skipped by design), 5 regression.</t>
+          <t>Local run on the D1-D6 change set: 644 unit+integration tests (29 files), 4 real-browser e2e, lint and typecheck clean. Last CI-verified baseline before the change set: run #7 (sha e06fbd7). CI for the change set: see the commit checks on the branch</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1569,17 +1561,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Low — none</t>
+          <t>Low - CI for this change set pending at time of writing</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Confirm CI green on the pushed commit</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>GitHub Actions run 37856267498</t>
+          <t>pnpm test; pnpm test:e2e; GitHub Actions</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1982,7 +1974,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>`role` (6 system, tenant custom roles, anti-escalation). DB seed ≡ contracts (tests/db/rls.test.ts 'seed data').</t>
+          <t>role table (system + per-organisation), 8 system roles incl. partner and manager (seed in migrations, kept in sync by tests/db/upgrade.test.ts and contracts.test.ts); anti-escalation at organisation, practice and company level; tests/api/permissions.test.ts</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2259,37 +2251,37 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Hierarchy: Organisation → Practice → Company → Accounting Period</t>
+          <t>Hierarchy: Platform -&gt; Organisation -&gt; Practice -&gt; Company -&gt; Accounting Period (practices and direct businesses on one engine)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Implemented as Organisation(type=PRACTICE|BUSINESS) → Company → Period. 'Practice' is a *type of organisation*, not a separate level; no practice entity (branches/offices/teams) exists.</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>CONFLICTING</t>
+          <t>practice table (PRACTICE organisations only), company.practice_id (composite FK + trigger), organisation.type immutable; migration 20260103000000; docs/architecture/v0-hierarchy-and-authorisation-design.md; tests/api/hierarchy.test.ts (D1 block), tests/db/hierarchy.test.ts (ownership integrity), tests/db/upgrade.test.ts (backfill)</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Medium — spec explicitly shows four levels; V7 (practice management: teams, review queues, client risk) likely needs a practice level distinct from tenant (e.g. one tenant, several practices/offices).</t>
+          <t>Low - resolved (ADR-23)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>DECISION REQUIRED: (a) keep 3-level and document that org.type=PRACTICE *is* the practice, or (b) add `practice` table between organisation and company. Cost of (b) rises sharply after V1.</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>ADR + migration test; tenancy sweep update</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2303,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Practice orgs own many companies; ASSIGNED scope per staff member; direct business = one-company org. tests/api/tenancy.test.ts (assigned-scope, auto-assign, two-org user).</t>
+          <t>Practice organisation -&gt; practices -&gt; many client companies; practice-level users reach only their practice's companies (tests/api/hierarchy.test.ts 'practice to client access'); direct business is a BUSINESS organisation with the same company/period API</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2331,7 +2323,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>tests/api/tenancy.test.ts</t>
+          <t>tests/api/hierarchy.test.ts, tests/api/tenancy.test.ts</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2823,37 +2815,37 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Generic states DRAFT → IN_PROGRESS → REVIEW → APPROVAL → COMPLETED → REJECTED</t>
+          <t>Generic states DRAFT -&gt; IN_PROGRESS -&gt; REVIEW -&gt; APPROVAL -&gt; COMPLETED -&gt; REJECTED</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Engine is definition-driven (packages/platform/src/workflow.ts). Registered definitions use different vocabularies: generic_approval = DRAFT/SUBMITTED/APPROVED/REJECTED/CANCELLED; ai_proposal_review = PENDING_REVIEW/APPROVED/REJECTED. The specified state set is not provided.</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>CONFLICTING</t>
+          <t>standard_workflow v1 in packages/contracts/src/workflow.ts; engine packages/platform/src/workflow.ts (versioned registry, per-transition permission for the instance's company, segregation across attempts, reopen/retry); tests/platform/workflow-engine.test.ts (16), tests/api/workflow-standard.test.ts (5); generic_approval kept for maker/checker</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Medium — later modules will assume the specified generic states; two vocabularies will leak into UI/reporting.</t>
+          <t>Low - resolved (ADR-25)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Add a `standard_workflow` definition with the exact spec states; keep generic_approval for maker/checker; document mapping</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Transition-matrix test for the new definition</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2969,32 +2961,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>No evidence attachment on workflow instances/transitions.</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>workflow_transition.evidence_document_ids (validated: exists in the organisation, same company or organisation-level, readable by the actor); evidenceRequired per transition; tests/platform/workflow-engine.test.ts 'evidence', tests/api/workflow-standard.test.ts</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>High — approvals without linked evidence defeat the audit/evidence-graph goals (Cross-Platform §6).</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Add `workflow_evidence` link (document/entity refs) + API (R2)</t>
+          <t>None (evidence-graph links, XP-06, still open)</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>API + isolation tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3008,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>approve/reject with permission check, optimistic concurrency, segregation-of-duties (requireDifferentFromStarter). Tested.</t>
+          <t>Dedicated workflow:approve permission, separation of duties (preparer/reviewer cannot approve, across attempts), mandatory comments; tests/platform/workflow-engine.test.ts, tests/api/workflow-standard.test.ts, tests/api/hierarchy.test.ts (approve on one company, not another)</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -3063,32 +3055,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Instances have no assignee/owner; no reassign action.</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>WorkflowEngine.reassign + POST /workflows/{id}/reassign: workflow:manage for the company, assignee must be able to work on it, recorded in history; tests/platform/workflow-engine.test.ts 'reassignment', tests/api/workflow-standard.test.ts</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Medium — review queues (V7/V8) require assignable work.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Add assignee + reassign transition + audit (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Workflow tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3854,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>RBAC (document:read/upload/archive) + company scope; downloads only for AVAILABLE; audited. No per-document/folder ACL or confidentiality level.</t>
+          <t>Company-level roles apply to documents (document:read/upload/archive evaluated for the document's own company; invisible = 404, no existence oracle); tests/api/hierarchy.test.ts 'unauthorised document access', tests/api/tenancy.test.ts. Per-document ACL / visibility classes still absent</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -3877,7 +3869,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Add visibility flag / ACL (R2)</t>
+          <t>Per-document visibility (restricted/confidential) - Tranche A4 remainder</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5037,7 +5029,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>DB: uk_app non-superuser, no BYPASSRLS, revoked UPDATE/DELETE on append-only tables (db tests). App: permission matrix. IAM: ECS task role scoped to the bucket/KMS, but `ses:SendEmail` on Resource `*` (region-conditioned).</t>
+          <t>Deny-by-default access resolution; four-level grants; anti-escalation; DB roles uk_migrator/uk_app; runtime role cannot disable RLS/triggers (tests/db/hierarchy.test.ts). AWS IAM least privilege unverified (never applied)</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -5319,7 +5311,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>tests/api/permissions.test.ts (147).</t>
+          <t>tests/api/permissions.test.ts (8 roles x 26 probes + escalation/last-owner/suspension), tests/api/hierarchy.test.ts, packages/contracts/src/authz.test.ts, tests/api/workflow-standard.test.ts</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
@@ -5413,7 +5405,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>tests/api/documents-jobs.test.ts, tenancy.test.ts (cross-tenant ids), infra pipeline (real clamd).</t>
+          <t>tests/api/hierarchy.test.ts 'unauthorised document access' (no-grant company, read-only grant, audited denials), tests/api/tenancy.test.ts, tests/api/documents-jobs.test.ts</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
@@ -6912,32 +6904,32 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>AI status vocabulary &amp; explainability</t>
+          <t>AI state vocabulary (V6: SUGGESTED -&gt; REVIEWED -&gt; ACCEPTED/REJECTED), explainability (prompt version, evidence, confidence) and privacy gate</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Spec V6: SUGGESTED → REVIEWED → ACCEPTED/REJECTED; store provider, prompt version, source evidence, confidence, recommendation, decision; no external AI without data-processing controls. Implemented: PENDING_REVIEW → APPROVED/REJECTED; no REVIEWED step, prompt version, evidence, confidence; **no per-tenant data-processing consent gate** before calling a provider.</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
-        <is>
-          <t>CONFLICTING</t>
+          <t>ai_proposal: SUGGESTED -&gt; UNDER_REVIEW -&gt; ACCEPTED | REJECTED (product-owner decision D3), provenance columns (provider, model, prompt_version, confidence, source_evidence), review/decision/application separated (recordApplication, DB check), packages/platform/src/ai.ts; tests/platform/ai-proposals.test.ts (7), tests/api/foundations.test.ts, tests/db/hierarchy.test.ts. Per-tenant AI data-processing gate NOT yet implemented</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Medium — vocabulary conflicts with V6; privacy gate is a legal control.</t>
+          <t>Medium - privacy gate missing (low until real providers are enabled)</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Align enum/workflow to V6; add org-level AI data-processing setting enforced in AiGateway (R7)</t>
+          <t>Add per-organisation AI data-processing setting + consent record before any external provider is enabled (Tranche B)</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>AI gateway tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -6946,8 +6938,384 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>CHG-D1</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Product-owner decision D1</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Distinct Practice entity; no separate engines; tenant isolation preserved; explicit practice-company relationship; no inconsistent ownership fields; documented ownership/billing/permission model</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>practice, practice_membership, company.practice_id (migration 20260103000000); v0-hierarchy-and-authorisation-design.md section 1; ADR-23; tests/api/hierarchy.test.ts, tests/db/hierarchy.test.ts</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Billing attaches to organisation only (documented; no billing code exists yet)</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>pnpm test</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>CHG-D2</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Product-owner decision D2</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Reusable workflow foundation: explicit transitions, permission per transition, actor/timestamp/audit, comments/evidence, rejection/reassignment/retry, no silent transitions, stricter controls possible</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>packages/platform/src/workflow.ts, packages/contracts/src/workflow.ts, DB trigger workflow_state_guard_trg (migration 20260103000100); ADR-25; tests/platform/workflow-engine.test.ts, tests/api/workflow-standard.test.ts, tests/db/hierarchy.test.ts</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>SLA/deadline (V0-4.7) still open</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>pnpm test</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>CHG-D3</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Product-owner decision D3</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>AI recommendations distinguishable from human actions; SUGGESTED -&gt; UNDER_REVIEW -&gt; ACCEPTED/REJECTED where appropriate; accepted result applied only through an authorised service; provenance persisted; per-use-case state machines documented</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>packages/platform/src/ai.ts, ai_proposal columns + checks, design doc section 7.2, ADR-26; tests/platform/ai-proposals.test.ts, tests/api/foundations.test.ts</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Per-tenant privacy gate: REV-13</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>pnpm test</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>CHG-D5</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Product-owner decision D5</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>One naming convention; clear organisation/practice/company/user-membership distinction; explicit FKs/uniques; data-preserving, reversible migrations; Prisma, migrations, tests, seeds, docs updated together</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>ADR-22; organisation_membership / practice_membership / company_membership; constraints and indexes renamed to &lt;table&gt;_&lt;cols&gt;_&lt;kind&gt;; Prisma schema, classification registry, docs; tests/db/upgrade.test.ts (populated upgrade + exact rollback); plural renaming deliberately NOT done (trade-off in ADR-22)</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Rename is metadata-only but flagged destructive-approved; single-release deploy (no old app against new schema)</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>pnpm test; tests/db/upgrade.test.ts</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>CHG-D6</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Product-owner decision D6</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Platform / organisation / practice / company authorisation, deny by default, least privilege, no cross-company leakage, central testable mechanism; tests for isolation, practice-to-client, multi-company users, differing roles, revoked memberships, document access, API enforcement</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>packages/contracts/src/authz.ts (pure rules), apps/api/src/common/access.ts (AccessContext), org.guard.ts; tables organisation_membership / practice_membership / company_membership; tests: packages/contracts/src/authz.test.ts (22), tests/api/hierarchy.test.ts (25), tests/db/hierarchy.test.ts (16), tests/api/permissions.test.ts (matrix for 8 system roles x 26 probes), tests/unit/architecture.test.ts (central-authoriser rules)</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Behaviour change documented: ASSIGNED members no longer auto-assigned companies they create</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>pnpm test</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>CHG-MIG1</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Review finding during implementation</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Migrations must work for a non-superuser owner (production uk_migrator): FORCE RLS applies to owners</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Found: the baseline seed INSERT failed (and later UPDATEs would have silently affected 0 rows) outside a superuser. Fixed in the two earlier un-deployed migrations and the new ones (NO FORCE / FORCE inside the transaction); ADR-27; tests/db/upgrade.test.ts 'non-superuser owner'. Not verified on a real RDS master user</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Medium (was High before the fix) - real RDS behaviour unverified</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Verify on first staging apply (Tranche C)</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>tests/db/upgrade.test.ts</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>CHG-MIG2</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Review finding during implementation</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Production migration runner must not demand a backup for a brand-new empty database but must for an upgrade</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>infra/db/migrate.sh detects a fresh database (first migration pending); tests/db/upgrade.test.ts proves it refuses the change set without BACKUP_SNAPSHOT_ID on a populated database and applies it with one</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>tests/db/upgrade.test.ts</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>CHG-DEF1</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Deliberately not built (scope)</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Cross-organisation engagement (a client business with its own organisation instructing a practice), billing/seat counting, UI for practices and grants, audit/job/integration company dimension</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Documented in the design doc (sections 1 and 8). The hierarchy allows adding an explicit grant table later without change</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Medium - needed before client-portal/billing work</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Plan with V7 (practice management) and V10/V11 (portal, billing)</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>Design review</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I137"/>
+  <autoFilter ref="A1:I145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6966,12 +7334,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Rows</t>
         </is>
@@ -6984,7 +7352,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -6994,7 +7362,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -7004,7 +7372,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -7014,7 +7382,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7034,7 +7402,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9">
@@ -7056,7 +7424,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -7066,7 +7434,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -7097,7 +7465,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7122,594 +7490,572 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Requirement ID</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Risk and impact</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Required action</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>MAN-TECH-09</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>High — encryption-at-rest, presigned-URL signature enforcement, KMS key policy, Object Lock and CORS are unverified on real S3. moto does not validate signatures.</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Run `pnpm test:infra` against a staging S3 bucket with INFRA_ENFORCES_SIGNATURES=1 (runbook infra-tests.md) before first production use</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>MAN-TECH-11</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>High — Manifest lists all four; a production incident could not be diagnosed from latency/error-rate/queue-depth signals.</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Implement OBS-02..05 (remediation R3)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>MAN-XVER-03</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>High — Manifest mandates flags for incomplete functionality; V1–V12 will ship incomplete modules, new tax rules and HMRC endpoints behind flags (Cross-Platform §9).</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Build flag service (env defaults + per-organisation overrides, audited, cached) before V1 (remediation R4)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>MAN-DOD-05</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>High — Definition of Done requires usable UI workflows; V0 foundations are API-only.</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Build V0 admin UI slices (R5); at minimum documents, tasks, notifications, members, audit</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>MAN-DOD-08</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>High — see OBS rows.</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>V0-3.1</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>High — V1 (VAT, currency, periods), V3 (Companies House) and V4 (CT/UTR) all need these attributes on the company record.</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Extend company profile (R1)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>V0-3.2</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>High — V1 blocker (Customers, Suppliers, Sales, Purchases).</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Build contacts module (R1)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>V0-3.3</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>High — needed by contacts, companies, invoices (V1) and filings (V3).</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Build addresses (R1)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>V0-3.4</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>High — V3 (Companies House) and V7 (KYC/AML, beneficial owners) depend on officers.</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Build officers/PSC model (R1)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>V0-3.5</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>High — V1 posting validates currency; multi-currency design must exist first.</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Add global reference table + seed + company base currency (R1)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>V0-3.9</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>High — period generation, V2 accounts and V3/V4 deadlines derive from the year-end.</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Add `year_end_month/day` (+ first period rules) to company profile (R1)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>V0-4.4</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>V0-6.1</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>High — see MAN-TECH-09; production ClamAV is not provisioned (REV-08).</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Real-S3 run + ClamAV service in Terraform</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>V0-6.10</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>High — V3 requires immutable filing evidence; governance mode can be bypassed by privileged principals and 30 days is short.</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Evidence class + COMPLIANCE-mode retain-until set by adapter + manifest hash (R2/R8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>V0-8.2</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>High — approvals without linked evidence defeat the audit/evidence-graph goals (Cross-Platform §6).</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Add `workflow_evidence` link (document/entity refs) + API (R2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>V0-6.1</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>High — accountant-grade audit trail needs field-level change history (esp. V1 master data, V4 tax).</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Add before/after (redacted) to audit API for update paths (R2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>V0-S6</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>High — see MAN-TECH-09; production ClamAV is not provisioned (REV-08).</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Real-S3 run + ClamAV service in Terraform</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>V0-6.10</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>High — see MAN-TECH-09.</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Real S3 validation (R8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>V0-S7</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>High — V3 requires immutable filing evidence; governance mode can be bypassed by privileged principals and 30 days is short.</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Evidence class + COMPLIANCE-mode retain-until set by adapter + manifest hash (R2/R8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>V0-8.2</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>High — documented ≠ recoverable. Documents (the evidence base) have versioning/Object Lock but no DR copy.</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Add S3 replication/backup for DR, run and record a restore drill in staging (R8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>XP-06</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>High — accountant-grade audit trail needs field-level change history (esp. V1 master data, V4 tax).</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Add before/after (redacted) to audit API for update paths (R2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>V0-S6</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>High (design) — retrofitting a link model after V1 data exists is costly; V0 §4 explicitly lists workflow 'evidence'.</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Add `evidence_link(src_type,src_id,dst_type,dst_id,kind)` with RLS now (R2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>XP-09</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>OBS-02</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>High — without access logs, incident triage and security forensics are blind.</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Add request-logging interceptor (route template, status, latency, correlation id; no PII) (R3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>OBS-03</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Prometheus/EMF metrics + dashboards (R3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>OBS-05</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>CloudWatch alarms (Terraform) + runbook (R3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>REV-04</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>High — real-S3 validation has never been performed.</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Staging run with INFRA_ENFORCES_SIGNATURES=1 (R8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>REV-05</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>High — see MAN-TECH-09.</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Real S3 validation (R8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>V0-S7</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>High — documented ≠ recoverable. Documents (the evidence base) have versioning/Object Lock but no DR copy.</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Add S3 replication/backup for DR, run and record a restore drill in staging (R8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>XP-06</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>High — plan/apply failures (quotas, IAM, KMS policy, name collisions, SES) are likely on first apply.</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>terraform plan in staging, apply, destroy/recreate cycle (R8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>REV-06</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>High (design) — retrofitting a link model after V1 data exists is costly; V0 §4 explicitly lists workflow 'evidence'.</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Add `evidence_link(src_type,src_id,dst_type,dst_id,kind)` with RLS now (R2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>XP-09</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>High — supply-chain controls absent; findings are low-exploitability (build-time) but would fail an audit gate.</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Pin patched versions via pnpm overrides/upgrade Next &amp; Prisma; restore `pnpm audit --audit-level=high`, add CodeQL, secret scanning, image scan (R0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>REV-08</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>OBS-02</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>High — without access logs, incident triage and security forensics are blind.</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Add request-logging interceptor (route template, status, latency, correlation id; no PII) (R3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>OBS-03</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Prometheus/EMF metrics + dashboards (R3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>OBS-05</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>CloudWatch alarms (Terraform) + runbook (R3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>REV-04</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>High — real-S3 validation has never been performed.</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Staging run with INFRA_ENFORCES_SIGNATURES=1 (R8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>REV-05</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>High — plan/apply failures (quotas, IAM, KMS policy, name collisions, SES) are likely on first apply.</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>terraform plan in staging, apply, destroy/recreate cycle (R8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>REV-06</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>High — supply-chain controls absent; findings are low-exploitability (build-time) but would fail an audit gate.</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Pin patched versions via pnpm overrides/upgrade Next &amp; Prisma; restore `pnpm audit --audit-level=high`, add CodeQL, secret scanning, image scan (R0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>REV-08</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>High — in production every upload would fail scanning and stay in SCANNING (fails closed, but the feature is unusable).</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Add ClamAV ECS service (+EFS signature cache or sidecar), service discovery, CLAMAV_HOST env, health alarm (R0)</t>
         </is>

--- a/docs/architecture/v0-compliance-matrix.xlsx
+++ b/docs/architecture/v0-compliance-matrix.xlsx
@@ -3149,27 +3149,27 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>`task.assignee_user_id` + `created_by_user_id`; assignee validated as active member with company access. tests/api/foundations.test.ts (tasks).</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>Owner = task.assignee_user_id (creator kept in created_by_user_id); assignee must be an active member who can read the task's company (apps/api/src/tasks/tasks.service.ts assertParticipant); semantics documented in v0-tranche-a.md section 6. tests/api/task-engine.test.ts (17), tests/api/task-review-security.test.ts (13), tests/db/task-engine.test.ts (6), tests/platform/task-reminders.test.ts (10), tests/db/privileges.test.ts (18), tests/db/upgrade.test.ts (task upgrade), tests/unit/architecture.test.ts (only the task service writes tasks)</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Low — 'owner' vs 'assignee' vs 'creator' semantics undefined; reassignment event only on change.</t>
+          <t>Low - none</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Clarify owner=assignee in ADR/OpenAPI</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Doc review</t>
+          <t>pnpm test (task suites)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>No reviewer field or review step.</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>task.reviewer_user_id + status IN_REVIEW; POST /tasks/{id}/review (APPROVE -&gt; DONE, RETURN -&gt; IN_PROGRESS with mandatory comment). Completion of a reviewed task only from IN_REVIEW and only by the designated reviewer - enforced in the service AND by trigger task_review_guard (migration 20260104000400/0500) reading the acting user from the tenant context. Reviewer != assignee (check), must hold workflow:review at nomination and at decision, assignee cannot change/remove own reviewer, decisions are conditional updates (no double-win), no dead end if the reviewer leaves. Verified against: spoofed body fields/headers, other organisation session, other tenant / system / user-only / no context, parallel decisions. tests/api/task-engine.test.ts (17), tests/api/task-review-security.test.ts (13), tests/db/task-engine.test.ts (6), tests/platform/task-reminders.test.ts (10), tests/db/privileges.test.ts (18), tests/db/upgrade.test.ts (task upgrade), tests/unit/architecture.test.ts (only the task service writes tasks)</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Medium — review/sign-off is central to V7/V8.</t>
+          <t>Low - resolved (ADR-31). Residual: database trusts the application-asserted user (same model as RLS); see security-architecture.md</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Add reviewer_user_id + review status (R2)</t>
+          <t>Production: separate DB credentials for API/worker, pgaudit</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Task tests</t>
+          <t>pnpm test (task-review-security, task-engine, db/task-engine)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Fields + API + OpenAPI; tests (create/complete/list filters).</t>
+          <t>Fields + API + OpenAPI; status set OPEN, IN_PROGRESS, IN_REVIEW, DONE, CANCELLED; filters status, assignee, reviewer, company, priority, source, dueBefore, overdue. tests/api/task-engine.test.ts (17), tests/api/task-review-security.test.ts (13), tests/db/task-engine.test.ts (6), tests/platform/task-reminders.test.ts (10), tests/db/privileges.test.ts (18), tests/db/upgrade.test.ts (task upgrade), tests/unit/architecture.test.ts (only the task service writes tasks)</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -3253,17 +3253,17 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Low — status set is OPEN/IN_PROGRESS/DONE/CANCELLED (no REVIEW).</t>
+          <t>Low - none</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Align with reviewer step</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>tests/api/foundations.test.ts</t>
+          <t>pnpm test; OpenAPI conformance (tests/api/openapi.test.ts)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>company_id with scope enforcement (assigned-scope tests).</t>
+          <t>task.company_id now a composite FK (organisation_id, company_id); per-company authorisation through the central authoriser for every sub-resource (404 for invisible companies). tests/api/task-engine.test.ts 'isolation', tests/db/task-engine.test.ts, tests/api/tenancy.test.ts, tests/api/hierarchy.test.ts</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3337,32 +3337,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>DB columns subject_type/subject_id exist but are not accepted by the create/update API or documented in OpenAPI.</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>task.source (MANUAL, WORKFLOW, AI_PROPOSAL, DOCUMENT, EVENT, SYSTEM; the last two reserved for the platform) + source_id; the referenced record must exist in the tenant and belong to the same company; filterable; in OpenAPI. tests/api/task-engine.test.ts 'source'</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Medium — 'source' (what created the task) is needed for exception-first UX and traceability.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Expose source in API; validate against known entity types (R2)</t>
+          <t>None (generic evidence graph, XP-06, is increment 7)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>API + OpenAPI tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3384,32 +3384,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>task_attachment: link to a document of the same company (trigger + API), unique, ACTIVE and readable by the caller; list shows names only to document readers; link/unlink audited; runtime role cannot UPDATE it. tests/api/task-engine.test.ts 'attachments' (3 cases), tests/db/privileges.test.ts</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Task↔document links (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>API tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3431,32 +3431,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>task_comment: append-only (trigger + no UPDATE/DELETE/TRUNCATE privilege), kinds COMMENT / REVIEW_APPROVED / REVIEW_RETURNED (a client cannot post a comment as an approval); managers, assignee and reviewer may comment; participants notified (task.commented). tests/api/task-engine.test.ts 'comments', tests/api/task-review-security.test.ts, tests/db/privileges.test.ts</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Add task_comment (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>API tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3478,32 +3478,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>None (BullMQ delayed jobs/scheduler available but unused).</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>task_reminder + TaskReminderSweeper (worker): system-context listing, one tenant transaction per reminder, FOR UPDATE SKIP LOCKED, notification and sent_at commit atomically; cancelled when the task finished; notification carries no task content; failures back off (30 s..1 h) and are abandoned after 8 attempts (audited). Verified: N parallel sweepers deliver exactly once, crash after notify rolls back, killed DB connection mid-transaction, cancel-vs-sweep race, poisoned reminder cannot starve others. tests/platform/task-reminders.test.ts (10), tests/api/task-engine.test.ts 'reminders'</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Medium — reminders drive deadlines/escalation.</t>
+          <t>Low - resolved (ADR-31). Limits: one-shot, in-app only (e-mail/SMS arrive with the channel port)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Reminder schedule + job + notification (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Job + notification tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Deny-by-default access resolution; four-level grants; anti-escalation; DB roles uk_migrator/uk_app; runtime role cannot disable RLS/triggers (tests/db/hierarchy.test.ts). AWS IAM least privilege unverified (never applied)</t>
+          <t>Deny-by-default access resolution; four-level grants; anti-escalation; DB roles uk_migrator/uk_app; effective-privilege matrix: runtime role is not superuser/BYPASSRLS, owns nothing, no SECURITY DEFINER helpers, cannot disable triggers/RLS or change grants, holds no UPDATE/DELETE/TRUNCATE on append-only tables (tests/db/privileges.test.ts, tests/db/hierarchy.test.ts). AWS IAM least privilege unverified (never applied)</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -7444,7 +7444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">

--- a/docs/architecture/v0-compliance-matrix.xlsx
+++ b/docs/architecture/v0-compliance-matrix.xlsx
@@ -3572,32 +3572,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>None (documents are a flat list; companyId filter only).</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>document_folder: tree per company or organisation (unique case-insensitive siblings, depth &lt;= 8, no cycles, same company as parent - trigger), folder follows document permissions, delete only when empty; documents list filters by folder. apps/api/src/documents/folders.service.ts. tests/api/document-management.test.ts (14), tests/db/document-management.test.ts (8), tests/api/document-ocr.test.ts (7), tests/api/evidence-graph.test.ts (8), tests/db/upgrade.test.ts (populated-database upgrade), tests/db/privileges.test.ts, tests/unit/architecture.test.ts</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Medium — practices organise by client/year/type.</t>
+          <t>Low - resolved. Folders organise, they do not secure (visibility is per document)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Folder/tree model with permissions inheritance (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>API + isolation tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3619,32 +3619,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Fixed fields only (name, class, content type, size, sha256, status). No user metadata/tags, document date, source, notes.</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>document.description, document_date, reference, labels (&lt;=10), metadata (&lt;=20 scalar keys, &lt;=8 KB; API + CHECK), PATCH /documents/{id} audited with before/after + reason; name search and filters. tests/api/document-management.test.ts (14), tests/db/document-management.test.ts (8), tests/api/document-ocr.test.ts (7), tests/api/evidence-graph.test.ts (8), tests/db/upgrade.test.ts (populated-database upgrade), tests/db/privileges.test.ts, tests/unit/architecture.test.ts</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Medium — needed for search and OCR results.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Add metadata JSON + tags (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>API tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3713,32 +3713,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>`document_class` free text (default GENERAL); no controlled taxonomy/retention mapping.</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>document_type REFERENCE table (16 seeded types, SELECT-only for the runtime role) with FK from document.document_class; registry in packages/contracts/src/documents.ts kept identical by tests/db/document-management.test.ts; unknown type = 422. tests/api/document-management.test.ts (14), tests/db/document-management.test.ts (8), tests/api/document-ocr.test.ts (7), tests/api/evidence-graph.test.ts (8), tests/db/upgrade.test.ts (populated-database upgrade), tests/db/privileges.test.ts, tests/unit/architecture.test.ts</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Medium — retention (S-08), OCR routing and filing evidence depend on controlled types.</t>
+          <t>Low - resolved. Per-type retention schedules belong to V0-S8</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Document-type reference table with retention + OCR hints (R2/R6)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Seed + API tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3807,32 +3807,32 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>No period link on documents.</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>document.period_id composite FK; trigger: the period must belong to the document's company; organisation-level documents cannot carry a period; filter by period. tests/api/document-management.test.ts (14), tests/db/document-management.test.ts (8), tests/api/document-ocr.test.ts (7), tests/api/evidence-graph.test.ts (8), tests/db/upgrade.test.ts (populated-database upgrade), tests/db/privileges.test.ts, tests/unit/architecture.test.ts</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Medium — V2/V4 evidence packs are per period.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Add accounting_period_id (composite FK) (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>DB + API tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3854,32 +3854,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Company-level roles apply to documents (document:read/upload/archive evaluated for the document's own company; invisible = 404, no existence oracle); tests/api/hierarchy.test.ts 'unauthorised document access', tests/api/tenancy.test.ts. Per-document ACL / visibility classes still absent</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>Company-level document permissions plus per-document visibility STANDARD/RESTRICTED: restricted = creator, explicit document_access grants, or document:confidential holders; everyone else gets 404 on documents, versions, downloads, edits, archive, task attachments/sources, workflow evidence, extraction and evidence links (AccessContext.canReadDocument/documentWhere, ADR-32); architecture test confines document reads to the four visibility-aware places; relaxing a restriction and managing grants need document:confidential. tests/api/document-management.test.ts (14), tests/db/document-management.test.ts (8), tests/api/document-ocr.test.ts (7), tests/api/evidence-graph.test.ts (8), tests/db/upgrade.test.ts (populated-database upgrade), tests/db/privileges.test.ts, tests/unit/architecture.test.ts</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Medium — client-visible vs internal documents (V7 portal) need document-level visibility.</t>
+          <t>Low - resolved (ADR-32). Per-folder ACL deliberately not provided</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Per-document visibility (restricted/confidential) - Tranche A4 remainder</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Authorisation tests</t>
+          <t>pnpm test (visibility block, permissions matrix)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3901,32 +3901,32 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Queue `documents`, process job, status machine, sniff+AV. No extraction hook, OCRProvider, derived-data store or confidence storage.</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>OcrProvider port + FakeOcrProvider (packages/platform/src/ocr.ts), OCR_PROVIDER=none|fake (fake refused in production), job document.ocr queued after a clean scan only when the organisation's documents.ocr flag is on and re-checked at run time, document_extraction store (status machine, final once SUCCEEDED, text &lt;=1 MB, confidence/pages/engine), text returned only on request and audited, never in audit/logs; retry + manual recovery tested. tests/api/document-management.test.ts (14), tests/db/document-management.test.ts (8), tests/api/document-ocr.test.ts (7), tests/api/evidence-graph.test.ts (8), tests/db/upgrade.test.ts (populated-database upgrade), tests/db/privileges.test.ts, tests/unit/architecture.test.ts</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Medium — OCR (V6) will need a place to attach derived data without touching immutable versions.</t>
+          <t>Low for the V0 requirement ('OCR-ready'). A real engine is a V6 deliverable behind the port</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Add `document_extraction` derived-data table + hook point (R7)</t>
+          <t>None for V0</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Job tests with fake OCR provider</t>
+          <t>pnpm test (document-ocr)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Version immutability trigger + hash; bucket Object Lock default GOVERNANCE 30 days (Terraform, **not applied/tested**). No 'filing evidence' class, no per-object COMPLIANCE retention, no evidence manifest.</t>
+          <t>DATABASE-ENFORCED: POST /documents/{id}/evidence-lock (evidence:lock) locks one AVAILABLE version with its SHA-256 and a retention date &gt;= 6 years; triggers refuse new versions, edits, archive, unlock, shortening retention and any change to the locked version; DELETE/TRUNCATE on document revoked from the runtime role; legal hold can be added never lifted (ADR-33). Object-level immutability (S3 Object Lock COMPLIANCE) is Terraform that has never been applied to a real account. tests/api/document-management.test.ts (14), tests/db/document-management.test.ts (8), tests/api/document-ocr.test.ts (7), tests/api/evidence-graph.test.ts (8), tests/db/upgrade.test.ts (populated-database upgrade), tests/db/privileges.test.ts, tests/unit/architecture.test.ts</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -3958,22 +3958,22 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>High — V3 requires immutable filing evidence; governance mode can be bypassed by privileged principals and 30 days is short.</t>
+          <t>Medium - application and database cannot alter locked evidence, but a privileged operator with bucket access could still delete the stored object until Object Lock is verified in AWS</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Evidence class + COMPLIANCE-mode retain-until set by adapter + manifest hash (R2/R8)</t>
+          <t>Production gate: apply and verify S3 Object Lock in COMPLIANCE mode in staging (REV-05)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Real-S3 Object Lock test in staging</t>
+          <t>pnpm test (evidence lock); staging verification</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4606,32 +4606,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>OcrProvider port, FakeOcrProvider, createOcrProvider(config) in packages/platform/src/ocr.ts; used by the document.ocr job (apps/worker/src/handlers/document.ts); tests/api/document-ocr.test.ts</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Medium — V6 prerequisite; interface should exist before documents pipeline is extended.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Add OCRProvider port + fake (R7)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Contract tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -5729,37 +5729,37 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Evidence graph (transaction ↔ document ↔ journal ↔ report ↔ tax return ↔ filing)</t>
+          <t>Evidence graph (transaction &lt;-&gt; document &lt;-&gt; journal &lt;-&gt; report &lt;-&gt; tax return &lt;-&gt; filing): generic, typed links with permissions and history</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>No generic evidence/link model. Only document↔company and (unexposed) task/workflow subject refs.</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>evidence_link: typed source-&gt;target, kinds SUPPORTS / DERIVED_FROM / ATTACHED_TO / REFERENCES / FILED_AS, same company, immutable (trigger), revoked with who/when/why and never deleted, partial unique index on active links; per-type resolvers check each end with its own permission (document visibility included); links to invisible entities are never listed; task attachments and workflow evidence write links in the same transaction; back-filled from existing data; /evidence-links API with evidence:read/manage; later versions append entity types (registry + resolver + CHECK) (ADR-34). tests/api/document-management.test.ts (14), tests/db/document-management.test.ts (8), tests/api/document-ocr.test.ts (7), tests/api/evidence-graph.test.ts (8), tests/db/upgrade.test.ts (populated-database upgrade), tests/db/privileges.test.ts, tests/unit/architecture.test.ts</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>High (design) — retrofitting a link model after V1 data exists is costly; V0 §4 explicitly lists workflow 'evidence'.</t>
+          <t>Low for V0. Polymorphic ends have no foreign keys: validated at write time and by an integrity test; entities are never hard-deleted</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Add `evidence_link(src_type,src_id,dst_type,dst_id,kind)` with RLS now (R2)</t>
+          <t>V1+ append their entity types (journal, bank_transaction, report, tax_return, filing)</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Isolation + API tests</t>
+          <t>pnpm test (evidence-graph, upgrade)</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>ai_proposal: SUGGESTED -&gt; UNDER_REVIEW -&gt; ACCEPTED | REJECTED (product-owner decision D3), provenance columns (provider, model, prompt_version, confidence, source_evidence), review/decision/application separated (recordApplication, DB check), packages/platform/src/ai.ts; tests/platform/ai-proposals.test.ts (7), tests/api/foundations.test.ts, tests/db/hierarchy.test.ts. Per-tenant AI data-processing gate NOT yet implemented</t>
+          <t>ai_proposal: SUGGESTED -&gt; UNDER_REVIEW -&gt; ACCEPTED | REJECTED (product-owner decision D3), provenance columns, review/decision/application separated (packages/platform/src/ai.ts); tests/platform/ai-proposals.test.ts, tests/api/foundations.test.ts. Per-organisation opt-in now exists for OCR (documents.ocr flag, default off) and AI suggestions (ai.beta flag, default off); a dedicated AI data-processing consent record is NOT yet implemented</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -7480,7 +7480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7778,51 +7778,51 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>V0-6.10</t>
+          <t>V0-8.2</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>High — V3 requires immutable filing evidence; governance mode can be bypassed by privileged principals and 30 days is short.</t>
+          <t>High — accountant-grade audit trail needs field-level change history (esp. V1 master data, V4 tax).</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Evidence class + COMPLIANCE-mode retain-until set by adapter + manifest hash (R2/R8)</t>
+          <t>Add before/after (redacted) to audit API for update paths (R2)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>V0-8.2</t>
+          <t>V0-S6</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>High — accountant-grade audit trail needs field-level change history (esp. V1 master data, V4 tax).</t>
+          <t>High — see MAN-TECH-09.</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Add before/after (redacted) to audit API for update paths (R2)</t>
+          <t>Real S3 validation (R8)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>V0-S6</t>
+          <t>V0-S7</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -7832,41 +7832,41 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>High — see MAN-TECH-09.</t>
+          <t>High — documented ≠ recoverable. Documents (the evidence base) have versioning/Object Lock but no DR copy.</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Real S3 validation (R8)</t>
+          <t>Add S3 replication/backup for DR, run and record a restore drill in staging (R8)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>V0-S7</t>
+          <t>XP-09</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>High — documented ≠ recoverable. Documents (the evidence base) have versioning/Object Lock but no DR copy.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Add S3 replication/backup for DR, run and record a restore drill in staging (R8)</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>XP-06</t>
+          <t>OBS-02</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -7876,19 +7876,19 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>High (design) — retrofitting a link model after V1 data exists is costly; V0 §4 explicitly lists workflow 'evidence'.</t>
+          <t>High — without access logs, incident triage and security forensics are blind.</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Add `evidence_link(src_type,src_id,dst_type,dst_id,kind)` with RLS now (R2)</t>
+          <t>Add request-logging interceptor (route template, status, latency, correlation id; no PII) (R3)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>XP-09</t>
+          <t>OBS-03</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -7903,14 +7903,14 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>Prometheus/EMF metrics + dashboards (R3)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>OBS-02</t>
+          <t>OBS-05</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -7920,19 +7920,19 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>High — without access logs, incident triage and security forensics are blind.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Add request-logging interceptor (route template, status, latency, correlation id; no PII) (R3)</t>
+          <t>CloudWatch alarms (Terraform) + runbook (R3)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>OBS-03</t>
+          <t>REV-04</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -7942,41 +7942,41 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High — real-S3 validation has never been performed.</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Prometheus/EMF metrics + dashboards (R3)</t>
+          <t>Staging run with INFRA_ENFORCES_SIGNATURES=1 (R8)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>OBS-05</t>
+          <t>REV-05</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High — plan/apply failures (quotas, IAM, KMS policy, name collisions, SES) are likely on first apply.</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>CloudWatch alarms (Terraform) + runbook (R3)</t>
+          <t>terraform plan in staging, apply, destroy/recreate cycle (R8)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>REV-04</t>
+          <t>REV-06</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -7986,76 +7986,32 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>High — real-S3 validation has never been performed.</t>
+          <t>High — supply-chain controls absent; findings are low-exploitability (build-time) but would fail an audit gate.</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Staging run with INFRA_ENFORCES_SIGNATURES=1 (R8)</t>
+          <t>Pin patched versions via pnpm overrides/upgrade Next &amp; Prisma; restore `pnpm audit --audit-level=high`, add CodeQL, secret scanning, image scan (R0)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>REV-05</t>
+          <t>REV-08</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>High — plan/apply failures (quotas, IAM, KMS policy, name collisions, SES) are likely on first apply.</t>
+          <t>High — in production every upload would fail scanning and stay in SCANNING (fails closed, but the feature is unusable).</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>terraform plan in staging, apply, destroy/recreate cycle (R8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>REV-06</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>High — supply-chain controls absent; findings are low-exploitability (build-time) but would fail an audit gate.</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Pin patched versions via pnpm overrides/upgrade Next &amp; Prisma; restore `pnpm audit --audit-level=high`, add CodeQL, secret scanning, image scan (R0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>REV-08</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>High — in production every upload would fail scanning and stay in SCANNING (fails closed, but the feature is unusable).</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Add ClamAV ECS service (+EFS signature cache or sidecar), service discovery, CLAMAV_HOST env, health alarm (R0)</t>
         </is>

--- a/docs/architecture/v0-compliance-matrix.xlsx
+++ b/docs/architecture/v0-compliance-matrix.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Structured pino logs with correlation ids (packages/core/src/logger.ts) and audit events exist. **No metrics, no tracing, no HTTP access log** (see OBS-02..05).</t>
+          <t>Structured pino logs with correlation + trace ids; access logs; metrics (Prometheus + EMF); readiness detail; trace-context propagation API -&gt; job -&gt; worker (W3C traceparent; job_record.trace_id); audit events. No OpenTelemetry spans/exporter (OBS-04, Tranche B). tests/api/observability.test.ts (12), packages/core/src/metrics.test.ts (5), tests/unit/observability-infra.test.ts (6), tests/unit/architecture.test.ts</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1044,22 +1044,22 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>High — Manifest lists all four; a production incident could not be diagnosed from latency/error-rate/queue-depth signals.</t>
+          <t>Medium - tracing spans, dashboards and SLOs are not part of V0 minimum</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Implement OBS-02..05 (remediation R3)</t>
+          <t>Tranche B: OpenTelemetry SDK + ADOT collector, dashboards, SLOs (OBS-04, XP-12)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Metrics endpoint/EMF + trace smoke test + dashboards</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>See MAN-TECH-11 / OBS-*.</t>
+          <t>Access logs, metrics, alarms-as-code, readiness detail and per-company job visibility delivered (see OBS-02/03/05); tracing and dashboards remain Tranche B</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -6157,32 +6157,32 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>No per-request log line (method, route, status, duration, tenant). Only errors/warnings are logged.</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>apps/api/src/common/access-log.middleware.ts: one structured line per request (method, route TEMPLATE, status, duration, bytes, correlation id, trace id, user, organisation; level by outcome; probes at debug; no bodies, headers, query strings or concrete ids; IP/user agent only when AUDIT_CAPTURE_DEVICE_METADATA). tests/api/observability.test.ts (12), packages/core/src/metrics.test.ts (5), tests/unit/observability-infra.test.ts (6), tests/unit/architecture.test.ts</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>High — without access logs, incident triage and security forensics are blind.</t>
+          <t>Low - resolved (ADR-35)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Add request-logging interceptor (route template, status, latency, correlation id; no PII) (R3)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>API test asserting log fields</t>
+          <t>pnpm test (observability)</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>None (no /metrics, no CloudWatch EMF). Queue depth, outbox lag, failed jobs, auth failures, p95 latency unmeasured.</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>MetricsRegistry (packages/core/src/metrics.ts) with Prometheus text (GET /metrics, 404 unless METRICS_TOKEN, bearer, constant-time) and CloudWatch EMF; http_requests_total / http_request_duration_seconds by route template + status class, auth_login_failures_total, outbox pending/failed/in-flight/lag, jobs by status (incl. DEAD), due reminders, worker heartbeat, event-loop lag, memory; label whitelist + 500-series cap. tests/api/observability.test.ts (12), packages/core/src/metrics.test.ts (5), tests/unit/observability-infra.test.ts (6), tests/unit/architecture.test.ts</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low for the V0 minimum. Real CloudWatch extraction is unproven until the first AWS apply; no dashboards (Tranche B)</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Prometheus/EMF metrics + dashboards (R3)</t>
+          <t>Staging: verify EMF extraction and build dashboards/SLOs</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Metrics endpoint test</t>
+          <t>pnpm test (observability, metrics)</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -6298,32 +6298,32 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>None — FAILED outbox events, DEAD jobs and throttle blocks are recorded but nobody is notified.</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>infra/terraform/observability.tf: SNS topic (+ e-mail subscription) and alarms for worker silence (missing data = breaching), FAILED outbox events, outbox lag, DEAD jobs, FAILED job backlog, API 5xx, rejected/throttled login bursts, ALB 5xx, unhealthy targets, ECS CPU/memory per service, RDS CPU/connections/free storage; METRICS_EMF=true for every service. Alarm&lt;-&gt;metric drift guarded by tests/unit/observability-infra.test.ts; terraform fmt/validate in CI. docs/runbooks/observability.md</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium - defined and validated, but never applied: delivery of alarms to a real inbox and EMF extraction are unproven</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>CloudWatch alarms (Terraform) + runbook (R3)</t>
+          <t>Production gate: apply in staging, subscribe, run a game-day (stop the worker, fill the DLQ)</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Alarm definitions in terraform validate; game-day</t>
+          <t>CI terraform job; staging game-day</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -7480,7 +7480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7536,51 +7536,51 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>MAN-TECH-11</t>
+          <t>MAN-XVER-03</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>High — Manifest lists all four; a production incident could not be diagnosed from latency/error-rate/queue-depth signals.</t>
+          <t>High — Manifest mandates flags for incomplete functionality; V1–V12 will ship incomplete modules, new tax rules and HMRC endpoints behind flags (Cross-Platform §9).</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Implement OBS-02..05 (remediation R3)</t>
+          <t>Build flag service (env defaults + per-organisation overrides, audited, cached) before V1 (remediation R4)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>MAN-XVER-03</t>
+          <t>MAN-DOD-05</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>High — Manifest mandates flags for incomplete functionality; V1–V12 will ship incomplete modules, new tax rules and HMRC endpoints behind flags (Cross-Platform §9).</t>
+          <t>High — Definition of Done requires usable UI workflows; V0 foundations are API-only.</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Build flag service (env defaults + per-organisation overrides, audited, cached) before V1 (remediation R4)</t>
+          <t>Build V0 admin UI slices (R5); at minimum documents, tasks, notifications, members, audit</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>MAN-DOD-05</t>
+          <t>MAN-DOD-08</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -7590,19 +7590,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>High — Definition of Done requires usable UI workflows; V0 foundations are API-only.</t>
+          <t>High — see OBS rows.</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Build V0 admin UI slices (R5); at minimum documents, tasks, notifications, members, audit</t>
+          <t>R3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>MAN-DOD-08</t>
+          <t>V0-3.1</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -7612,41 +7612,41 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>High — see OBS rows.</t>
+          <t>High — V1 (VAT, currency, periods), V3 (Companies House) and V4 (CT/UTR) all need these attributes on the company record.</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>Extend company profile (R1)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>V0-3.1</t>
+          <t>V0-3.2</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>High — V1 (VAT, currency, periods), V3 (Companies House) and V4 (CT/UTR) all need these attributes on the company record.</t>
+          <t>High — V1 blocker (Customers, Suppliers, Sales, Purchases).</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Extend company profile (R1)</t>
+          <t>Build contacts module (R1)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>V0-3.2</t>
+          <t>V0-3.3</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -7656,19 +7656,19 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>High — V1 blocker (Customers, Suppliers, Sales, Purchases).</t>
+          <t>High — needed by contacts, companies, invoices (V1) and filings (V3).</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Build contacts module (R1)</t>
+          <t>Build addresses (R1)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>V0-3.3</t>
+          <t>V0-3.4</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -7678,19 +7678,19 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>High — needed by contacts, companies, invoices (V1) and filings (V3).</t>
+          <t>High — V3 (Companies House) and V7 (KYC/AML, beneficial owners) depend on officers.</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Build addresses (R1)</t>
+          <t>Build officers/PSC model (R1)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>V0-3.4</t>
+          <t>V0-3.5</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -7700,19 +7700,19 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>High — V3 (Companies House) and V7 (KYC/AML, beneficial owners) depend on officers.</t>
+          <t>High — V1 posting validates currency; multi-currency design must exist first.</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Build officers/PSC model (R1)</t>
+          <t>Add global reference table + seed + company base currency (R1)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>V0-3.5</t>
+          <t>V0-3.9</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -7722,85 +7722,85 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>High — V1 posting validates currency; multi-currency design must exist first.</t>
+          <t>High — period generation, V2 accounts and V3/V4 deadlines derive from the year-end.</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Add global reference table + seed + company base currency (R1)</t>
+          <t>Add `year_end_month/day` (+ first period rules) to company profile (R1)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>V0-3.9</t>
+          <t>V0-6.1</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>High — period generation, V2 accounts and V3/V4 deadlines derive from the year-end.</t>
+          <t>High — see MAN-TECH-09; production ClamAV is not provisioned (REV-08).</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Add `year_end_month/day` (+ first period rules) to company profile (R1)</t>
+          <t>Real-S3 run + ClamAV service in Terraform</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>V0-6.1</t>
+          <t>V0-8.2</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>High — see MAN-TECH-09; production ClamAV is not provisioned (REV-08).</t>
+          <t>High — accountant-grade audit trail needs field-level change history (esp. V1 master data, V4 tax).</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Real-S3 run + ClamAV service in Terraform</t>
+          <t>Add before/after (redacted) to audit API for update paths (R2)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>V0-8.2</t>
+          <t>V0-S6</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>High — accountant-grade audit trail needs field-level change history (esp. V1 master data, V4 tax).</t>
+          <t>High — see MAN-TECH-09.</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Add before/after (redacted) to audit API for update paths (R2)</t>
+          <t>Real S3 validation (R8)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>V0-S6</t>
+          <t>V0-S7</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -7810,41 +7810,41 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>High — see MAN-TECH-09.</t>
+          <t>High — documented ≠ recoverable. Documents (the evidence base) have versioning/Object Lock but no DR copy.</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Real S3 validation (R8)</t>
+          <t>Add S3 replication/backup for DR, run and record a restore drill in staging (R8)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>V0-S7</t>
+          <t>XP-09</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>High — documented ≠ recoverable. Documents (the evidence base) have versioning/Object Lock but no DR copy.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Add S3 replication/backup for DR, run and record a restore drill in staging (R8)</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>XP-09</t>
+          <t>REV-04</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -7854,41 +7854,41 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High — real-S3 validation has never been performed.</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>Staging run with INFRA_ENFORCES_SIGNATURES=1 (R8)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>OBS-02</t>
+          <t>REV-05</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>High — without access logs, incident triage and security forensics are blind.</t>
+          <t>High — plan/apply failures (quotas, IAM, KMS policy, name collisions, SES) are likely on first apply.</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Add request-logging interceptor (route template, status, latency, correlation id; no PII) (R3)</t>
+          <t>terraform plan in staging, apply, destroy/recreate cycle (R8)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>OBS-03</t>
+          <t>REV-06</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -7898,19 +7898,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High — supply-chain controls absent; findings are low-exploitability (build-time) but would fail an audit gate.</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Prometheus/EMF metrics + dashboards (R3)</t>
+          <t>Pin patched versions via pnpm overrides/upgrade Next &amp; Prisma; restore `pnpm audit --audit-level=high`, add CodeQL, secret scanning, image scan (R0)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>OBS-05</t>
+          <t>REV-08</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -7920,98 +7920,10 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High — in production every upload would fail scanning and stay in SCANNING (fails closed, but the feature is unusable).</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>CloudWatch alarms (Terraform) + runbook (R3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>REV-04</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>High — real-S3 validation has never been performed.</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Staging run with INFRA_ENFORCES_SIGNATURES=1 (R8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>REV-05</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>High — plan/apply failures (quotas, IAM, KMS policy, name collisions, SES) are likely on first apply.</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>terraform plan in staging, apply, destroy/recreate cycle (R8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>REV-06</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>High — supply-chain controls absent; findings are low-exploitability (build-time) but would fail an audit gate.</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Pin patched versions via pnpm overrides/upgrade Next &amp; Prisma; restore `pnpm audit --audit-level=high`, add CodeQL, secret scanning, image scan (R0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>REV-08</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>High — in production every upload would fail scanning and stay in SCANNING (fails closed, but the feature is unusable).</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Add ClamAV ECS service (+EFS signature cache or sidecar), service discovery, CLAMAV_HOST env, health alarm (R0)</t>
         </is>

--- a/docs/architecture/v0-compliance-matrix.xlsx
+++ b/docs/architecture/v0-compliance-matrix.xlsx
@@ -10,9 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High-risk findings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision register" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope proposals" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matrix'!$A$1:$I$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matrix'!$A$1:$N$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Decision register'!$A$1:$N$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +72,26 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -96,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -118,6 +141,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -485,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -497,6 +532,11 @@
     <col width="46" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,6 +585,31 @@
           <t>Severity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Recommendation (open rows)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Blocks V1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Blocks production</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -592,6 +657,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -639,6 +709,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -686,6 +761,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -733,6 +813,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -780,6 +865,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -827,6 +917,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -846,7 +941,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>packages/contracts/src/authz.ts (pure rules), apps/api/src/common/access.ts (AccessContext), org.guard.ts; tables organisation_membership / practice_membership / company_membership; tests: packages/contracts/src/authz.test.ts (22), tests/api/hierarchy.test.ts (25), tests/db/hierarchy.test.ts (16), tests/api/permissions.test.ts (matrix for 8 system roles x 26 probes), tests/unit/architecture.test.ts (central-authoriser rules)</t>
+          <t>packages/contracts/src/authz.ts (pure rules), apps/api/src/common/access.ts (AccessContext), org.guard.ts; tables organisation_membership / practice_membership / company_membership; tests: packages/contracts/src/authz.test.ts (22), tests/api/hierarchy.test.ts (25), tests/db/hierarchy.test.ts (16), tests/api/permissions.test.ts (matrix for 8 system roles x 32 probes), tests/unit/architecture.test.ts (central-authoriser rules)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -874,6 +969,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -921,6 +1021,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -968,6 +1073,31 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d)</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1015,6 +1145,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1062,6 +1197,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Included in OBS-04 + dashboards (S)</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1109,6 +1269,31 @@
           <t>None</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Design input</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1156,6 +1341,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1203,6 +1393,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1250,6 +1445,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1269,34 +1469,39 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>No feature-flag mechanism exists anywhere (grep for feature flags in apps/packages/infra: none).</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>packages/contracts/src/features.ts (registry: ai.beta, documents.ocr, tax.rules.next, hmrc.endpoints.new, filing.formats.new, reporting.standards.new - all default off; undeclared flags cannot be read or set), packages/platform/src/features.ts (FeatureFlagService: organisation override &gt; FEATURE_FLAG_DEFAULTS &gt; default, TTL cache), table feature_flag_override (RLS), GET/PUT/DELETE /feature-flags (org:manage, audited with reason), @RequireFeature + FeatureGuard, re-checked inside jobs (ai.suggest, document.ocr). Tests: tests/api/feature-flags.test.ts (8), tests/platform/feature-flag-service.test.ts (4), packages/contracts/src/features.test.ts (5)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>High — Manifest mandates flags for incomplete functionality; V1–V12 will ship incomplete modules, new tax rules and HMRC endpoints behind flags (Cross-Platform §9).</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Build flag service (env defaults + per-organisation overrides, audited, cached) before V1 (remediation R4)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Unit + API tests for flag resolution/overrides/audit</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1316,7 +1521,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>packages/db/prisma/migrations (4).</t>
+          <t>16 migrations in packages/db/prisma/migrations (baseline through 20260104000900), additive or data-preserving (one forward-only enum value, documented); applied from scratch with the production script in CI (job 'migrations-from-scratch'), as a non-superuser owner, and onto populated databases (data preserved, FK validation under forced RLS covered): tests/db/upgrade.test.ts (6), tests/unit/migrations.test.ts (18); docs/runbooks/migrations.md</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1344,6 +1549,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1391,6 +1601,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1438,6 +1653,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1457,34 +1677,39 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Audit written in-transaction for auth, org, company, period, document, task, integration, workflow-adjacent actions (tests/api/*). Content gaps: see V0-8.2/8.4/8.5.</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>Audit events exist for authentication, organisation, company, period, document, folder, task, review, evidence, feature-flag, integration and workflow actions, written in the business transaction, append-only by privilege AND trigger. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (21) (append-only privileges), tests/db/rls.test.ts (27)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Medium — events exist but lack before/after, reason and source workflow.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Close V0-8 gaps (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Audit tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1532,6 +1757,31 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Decision needed</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>XL (3-4 w for documents, tasks, workflows, notifications, members, integrations, AI proposals, audit)</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1551,7 +1801,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Local run on the D1-D6 change set: 644 unit+integration tests (29 files), 4 real-browser e2e, lint and typecheck clean. Last CI-verified baseline before the change set: run #7 (sha e06fbd7). CI for the change set: see the commit checks on the branch</t>
+          <t>Verified commit a57ebb3: CI run https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37901071296 - all 9 jobs green (build/lint/typecheck/unit/integration/e2e; real S3 protocol + real ClamAV; dependency audit + secret scan; migrations from scratch; terraform fmt/init/validate; images api, worker, web, migrate with Trivy) plus CodeQL; clean-clone: fresh git clone, pnpm install --frozen-lockfile, build, typecheck, lint, 956/956 unit+integration tests (51 files), 4/4 real-browser e2e tests, OpenAPI regeneration without drift. Local: 956 unit+integration tests passed (51 files), 0 failed, 0 skipped.</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1561,17 +1811,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Low - CI for this change set pending at time of writing</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Confirm CI green on the pushed commit</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>pnpm test; pnpm test:e2e; GitHub Actions</t>
+          <t>GitHub Actions; pnpm test; pnpm test:e2e</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1579,6 +1829,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1626,6 +1881,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1673,6 +1933,31 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Included in OBS-04/OBS-05</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1720,6 +2005,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1767,6 +2057,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1814,6 +2109,31 @@
           <t>None</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>V6-V12</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1861,6 +2181,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1908,6 +2233,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1955,6 +2285,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2002,6 +2337,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2021,7 +2361,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Permission catalogue is code (`packages/contracts/src/permissions.ts`, 26 permissions) and `role.permissions text[]`. There is no `permissions` table.</t>
+          <t>Permission catalogue is code (`packages/contracts/src/permissions.ts`, 38 permissions) and `role.permissions text[]`. There is no `permissions` table.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -2047,6 +2387,31 @@
       <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Low</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -2096,6 +2461,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2143,6 +2513,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2190,6 +2565,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2237,6 +2617,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Recommended (new-device alert)</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>M (4 d)</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release) / V7 client portal</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2284,6 +2689,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2331,6 +2741,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2378,6 +2793,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2397,34 +2817,39 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>`company`: name, company_number, legal_form, status. Missing: registered/trading address, incorporation date, company status (CH), accounting reference date/year-end, VAT/UTR/PAYE references, SIC codes, jurisdiction, base currency.</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>company profile: incorporation date, financial year-end, base currency, country, tax jurisdiction, practice, legal form, status; PATCH /companies/{id} validated against reference data and audited with before/after; addresses via address table; GET /companies/{id}/periods/next derives the next period. VAT/UTR/PAYE references and Companies House status are owned by V3/V4/V5 with their own lawful basis. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>High — V1 (VAT, currency, periods), V3 (Companies House) and V4 (CT/UTR) all need these attributes on the company record.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Extend company profile (R1)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Migration + API + tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2444,34 +2869,39 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>No contacts table or API (customers/suppliers in V1 depend on it).</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>contact (PERSON/ORGANISATION, organisation-level or company-level, archive/restore, labels, search), contact:read/manage COMPANY-scope permissions. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>High — V1 blocker (Customers, Suppliers, Sales, Purchases).</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Build contacts module (R1)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Tenant-isolation + RBAC + OpenAPI tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2491,34 +2921,39 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>address owned by exactly one company or contact (DB check), kinds, one primary per owner+kind (partial unique index), UK postcode validated in API and database. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>High — needed by contacts, companies, invoices (V1) and filings (V3).</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Build addresses (R1)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>As above</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2538,34 +2973,39 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>company_officer: contact appointed to an office with appointed/resigned dates, history kept, contact must be organisation-level or the same company's (trigger). Data-minimised (no date of birth or nationality until V3). migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>High — V3 (Companies House) and V7 (KYC/AML, beneficial owners) depend on officers.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Build officers/PSC model (R1)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>As above</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2585,34 +3025,39 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>None (no ISO 4217 reference data, no company base currency).</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>currency REFERENCE table seeded from system ISO 4217 data (159 transactional codes), company base_currency FK (default GBP), SELECT-only for the runtime role. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>High — V1 posting validates currency; multi-currency design must exist first.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Add global reference table + seed + company base currency (R1)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Seed-integrity + API tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2632,34 +3077,39 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>country REFERENCE table seeded from ISO 3166-1 (249), alpha-2/alpha-3/numeric, company country FK. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Medium — addresses/contacts/VAT place-of-supply.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Global reference table + seed (R1)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Seed-integrity test</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2679,34 +3129,39 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>None. (Manifest requires effective-dated tax/reporting rules from V1.)</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>tax_jurisdiction: effective-dated (valid_from/valid_to, exclusion constraint so a code never overlaps itself), GB-HMRC and IE-REV seeded, `?asOf=` query, company tax_jurisdiction_code FK. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Medium — design of effective-dated reference data should be fixed before V1/V4/V5.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Add `tax_jurisdiction` with effective dating + pattern for versioned rule sets (R1)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Effective-dating tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2754,6 +3209,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2773,34 +3233,39 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>No company-level accounting reference date / year-end; periods are created manually with free dates.</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>company year_end_month/day (29 Feb = last day of February; CHECK with NOT NULL guards), pure nextAccountingPeriod() (no gap, no overlap, leap years), GET /companies/{id}/periods/next. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>High — period generation, V2 accounts and V3/V4 deadlines derive from the year-end.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Add `year_end_month/day` (+ first period rules) to company profile (R1)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Unit tests for period generation</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2848,6 +3313,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2895,6 +3365,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2942,6 +3417,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2989,6 +3469,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3036,6 +3521,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3083,6 +3573,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3130,6 +3625,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE V1</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Yes (recommended)</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d)</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Pre-V1 gate</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3177,6 +3697,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3224,6 +3749,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3271,6 +3801,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3318,6 +3853,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3365,6 +3905,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3412,6 +3957,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3459,6 +4009,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3506,6 +4061,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3553,6 +4113,31 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>S + REV-08</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3600,6 +4185,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3647,6 +4237,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3694,6 +4289,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3741,6 +4341,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3788,6 +4393,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3835,6 +4445,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3882,6 +4497,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3929,6 +4549,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3976,6 +4601,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>S (1 d)</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4023,6 +4673,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d)</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4070,6 +4745,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4117,6 +4797,31 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE V1</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Yes (recommended)</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>S-M (3 d)</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Pre-V1 gate</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4164,6 +4869,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4183,34 +4893,39 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Only free-form `metadata`; no structured before/after.</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>Structured before/after (changed fields only, redacted, size-capped) on company, task, document, contact, officer, membership, feature-flag and workflow actions. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (21) (append-only privileges), tests/db/rls.test.ts (27)</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>High — accountant-grade audit trail needs field-level change history (esp. V1 master data, V4 tax).</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Add before/after (redacted) to audit API for update paths (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Audit content tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4258,6 +4973,31 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>S (1 d) + legal input</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4277,34 +5017,39 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>No `reason` field (e.g. why a period was reopened).</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>Optional reason on audited actions (member removal, archive, feature-flag change, document edit); mandatory for decisions: task returns, evidence locks and evidence-link revocation. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (21) (append-only privileges), tests/db/rls.test.ts (27)</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Add optional reason, mandatory on sensitive actions (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Audit tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4324,34 +5069,39 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>No workflow/correlation linkage field (correlation_id exists).</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>source_workflow_id recorded when the action is part of a workflow (workflow transitions, AI proposal application); correlation id on every event. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (21) (append-only privileges), tests/db/rls.test.ts (27)</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Add workflow_instance_id reference (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Audit tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4399,6 +5149,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4446,6 +5201,31 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>n/a for V0</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>V3 (Companies House), V4/V5 (HMRC), V11 (banks, Xero, QuickBooks, FreeAgent, Stripe, Shopify, payroll)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4493,6 +5273,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4540,6 +5325,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE V1</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Yes (recommended)</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>S (1 d)</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Pre-V1 gate</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4587,6 +5397,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4634,6 +5449,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4681,6 +5501,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>S (1-2 d) if done now</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>V6 (OCR/AI) - or the Pre-V1 gate if you want V0 spec-complete</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4700,34 +5545,39 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>`ai_run` table (hashes of input/output, provider, model, tokens, latency, status, correlation id); append-only. Name differs from `ai_requests`; no prompt-version / source-evidence / confidence fields (V6 explainability).</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>ai_run: hashed input/output, provider, model, tokens, latency, status, correlation id, append-only (privileges + trigger); AI requests are permission-aware (ai:use / ai:approve, company scope) and behind the ai.beta flag; explainability (prompt version, confidence, source evidence) lives on ai_proposal (D3). Table name ai_run (singular convention D5). Tests: tests/platform/ai-proposals.test.ts, tests/api/foundations.test.ts (AI block), tests/api/feature-flags.test.ts (8)</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Medium — V6 requires prompt version, evidence and confidence.</t>
+          <t>Low. External-provider privacy gate tracked under REV-13</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Add prompt_version, evidence refs, confidence columns (R7)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>AI tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4775,6 +5625,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4822,6 +5677,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4869,6 +5729,31 @@
           <t>—</t>
         </is>
       </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4916,6 +5801,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>S (1-2 d)</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4963,6 +5873,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>S (1 d)</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4982,7 +5917,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>See MAN-TECH-08.</t>
+          <t>Forced row-level security on every tenant table (registry == database, classification test), composite (organisation_id, id) foreign keys, tenant context set per transaction, runtime role without BYPASSRLS that owns nothing; tests: tests/db/rls.test.ts (27), tests/db/classification.test.ts (93), tests/api/tenancy.test.ts (21), tests/db/privileges.test.ts (21), tests/unit/architecture.test.ts (16) (no code path bypasses the tenant context). Residual trust boundary documented: the database trusts the application to assert tenant and user</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -5010,6 +5945,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5057,6 +5997,31 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>M (3 d)</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5076,34 +6041,39 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Secret-pattern scan of tracked files clean; secrets injected from AWS Secrets Manager (Terraform); `.env.example` has blanks. Test-only keys live in vitest.config.ts. **No automated secret scanning in CI.**</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>gitleaks secret scan in CI (job 'dependency audit + secret scan', green on a57ebb3), .gitleaks.toml, secrets from AWS Secrets Manager (Terraform), `.env.example` has blanks, config validation refuses unsafe production settings (packages/core/src/config.test.ts). Repository push protection is a GitHub setting the repository owner must enable (not verifiable here)</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Medium — a future accidental commit would not be caught.</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Add gitleaks/GitHub secret scanning + push protection (R0)</t>
+          <t>Owner: enable GitHub secret-scanning push protection</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>CI job</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -5151,6 +6121,31 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>Included in MAN-TECH-09</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5198,6 +6193,31 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>M (3-4 d)</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -5245,6 +6265,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE V1</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Partly: classification only</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>L (7-8 d), split S + M/L</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Pre-V1 gate (policy + classification), Tranche B (parallel with V1, before first production release) (purge jobs)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -5292,6 +6337,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -5311,7 +6361,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>tests/api/permissions.test.ts (8 roles x 26 probes + escalation/last-owner/suspension), tests/api/hierarchy.test.ts, packages/contracts/src/authz.test.ts, tests/api/workflow-standard.test.ts</t>
+          <t>tests/api/permissions.test.ts (8 roles x 32 probes + escalation/last-owner/suspension), tests/api/hierarchy.test.ts, packages/contracts/src/authz.test.ts, tests/api/workflow-standard.test.ts</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
@@ -5339,6 +6389,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -5358,34 +6413,39 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Asserted across auth, company, document, workflow, AI, integration tests; append-only in rls.test.ts. No test of before/after/reason (not implemented).</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>Audit creation asserted across auth, company, document, task, workflow, AI, integration, feature-flag and evidence tests; before/after/reason/source-workflow asserted in the audit framework tests; append-only asserted by privilege matrix and triggers. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (21) (append-only privileges), tests/db/rls.test.ts (27)</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Medium — follows V0-8.2/8.4.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Extend when audit fields are added</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>tests/api/*</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -5433,6 +6493,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -5480,6 +6545,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -5527,6 +6597,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE V1</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Yes (recommended)</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>Included in V0-9.4</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Pre-V1 gate</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -5574,6 +6669,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -5621,6 +6721,31 @@
           <t>None</t>
         </is>
       </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>V1+</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -5668,6 +6793,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Design decision</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>M design</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>V1 design / V10</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -5715,6 +6865,31 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>V1+</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -5762,6 +6937,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -5809,6 +6989,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -5828,27 +7013,27 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>job_record has status, attempts, error, correlation_id, organisation_id, timestamps; API shows them without payload. **No company_id.**</t>
-        </is>
-      </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>job_record has status, attempts, error, correlation id, trace id, organisation and company (migration 20260104000900); GET /jobs[?companyId&amp;status] hides jobs of companies the caller cannot read; payloads never returned; DEAD/FAILED counted in metrics and alarmed. Tests: tests/api/observability.test.ts (12), tests/api/documents-jobs.test.ts (17), tests/jobs/jobs.test.ts (14)</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Low — company-level job views (practice dashboards) cannot filter.</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Add company_id to job_record (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Jobs API tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -5856,6 +7041,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -5875,34 +7065,39 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>None — see MAN-XVER-03.</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>packages/contracts/src/features.ts (registry: ai.beta, documents.ocr, tax.rules.next, hmrc.endpoints.new, filing.formats.new, reporting.standards.new - all default off; undeclared flags cannot be read or set), packages/platform/src/features.ts (FeatureFlagService: organisation override &gt; FEATURE_FLAG_DEFAULTS &gt; default, TTL cache), table feature_flag_override (RLS), GET/PUT/DELETE /feature-flags (org:manage, audited with reason), @RequireFeature + FeatureGuard, re-checked inside jobs (ai.suggest, document.ocr). Tests: tests/api/feature-flags.test.ts (8), tests/platform/feature-flag-service.test.ts (4), packages/contracts/src/features.test.ts (5)</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Flag tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -5950,6 +7145,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE V1</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Partly (same split as V0-S8)</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>Included in V0-S8</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Pre-V1 gate / Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -5997,6 +7217,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>M (with the UI slices)</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6044,6 +7289,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>M (4 d)</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -6091,6 +7361,31 @@
           <t>None</t>
         </is>
       </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -6138,6 +7433,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -6185,6 +7485,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -6232,6 +7537,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -6279,6 +7589,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>M (4 d)</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -6326,6 +7661,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d) in staging</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -6373,6 +7733,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -6392,34 +7757,39 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Event row in the business transaction; PENDING→PUBLISHED; retry_count/last_error/backoff/FAILED/replay; SKIP LOCKED multi-relay; consumer idempotency via event_consumption; immutable content; tenant isolation (13 unit-level + 4 integration tests). Gaps: **no per-aggregate ordering** (BullMQ concurrency 5; two events for one aggregate can be handled out of order), **no retention/cleanup** of PUBLISHED events, no relay-lag metric/alert, FAILED events need manual replay.</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>Outbox hardening (ADR-29): per-aggregate ordering (seq + head-only relay + consumer ordering guard), processed_at, guarded cleanup (unprocessed events undeletable by trigger), lag/backlog stats exposed as metrics and alarms, replay of FAILED events; FAILED head blocks only its own aggregate. Tests: tests/platform/outbox-hardening.test.ts (12), tests/platform/outbox.test.ts (13), tests/api/foundations.test.ts (23) (end-to-end consumers), tests/api/observability.test.ts (12) (lag/failed gauges and readiness)</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Medium (becomes High with V1) — ledger/posting consumers need ordered delivery per aggregate.</t>
+          <t>Low - resolved. Liveness trade-off documented: a poisoned head event blocks its own aggregate until replayed (alarmed)</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Add ordering key (per-aggregate sequence or queue group) + cleanup job + lag metric before V1 consumers (R6/R3)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Ordering test with concurrent consumers</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -6467,6 +7837,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -6514,6 +7889,31 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d)</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -6561,6 +7961,31 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>M (3-4 d)</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -6580,34 +8005,39 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>`pnpm audit --prod`: 5 findings (3 high, 2 moderate): postcss (via next, build-time CSS processing) ×4 and deepmerge-ts (via prisma CLI config). The audit gate present in the first CI draft was dropped in the rewrite; **CI currently has no audit, SAST (CodeQL) or container scan.**</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>CI job 'dependency audit + secret scan' (https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37901071296) runs `pnpm audit --audit-level=high`; local `pnpm audit --prod --audit-level=high`: no known vulnerabilities; pnpm overrides for postcss/deepmerge-ts; Vitest 4; CodeQL workflow (green on the verified commit); gitleaks; dependency-review on pull requests; Dependabot; Trivy HIGH/CRITICAL gate on all four images (green). docs/runbooks/supply-chain.md</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>High — supply-chain controls absent; findings are low-exploitability (build-time) but would fail an audit gate.</t>
+          <t>Low - resolved. Repository settings that cannot be verified from code: GitHub push protection and branch protection</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Pin patched versions via pnpm overrides/upgrade Next &amp; Prisma; restore `pnpm audit --audit-level=high`, add CodeQL, secret scanning, image scan (R0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>CI job output</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -6655,6 +8085,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>S (1 d)</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -6702,6 +8157,31 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>Yes (hard blocker)</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>M (3 d)</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -6749,6 +8229,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>S (0.5 d)</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -6796,6 +8301,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d)</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -6843,6 +8373,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>S-M (2-3 d)</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -6890,6 +8445,31 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>S (1-2 d)</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -6937,6 +8517,31 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>Yes (before any external AI provider)</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d)</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -6984,6 +8589,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -7031,6 +8641,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -7078,6 +8693,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -7125,6 +8745,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -7144,7 +8769,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>packages/contracts/src/authz.ts (pure rules), apps/api/src/common/access.ts (AccessContext), org.guard.ts; tables organisation_membership / practice_membership / company_membership; tests: packages/contracts/src/authz.test.ts (22), tests/api/hierarchy.test.ts (25), tests/db/hierarchy.test.ts (16), tests/api/permissions.test.ts (matrix for 8 system roles x 26 probes), tests/unit/architecture.test.ts (central-authoriser rules)</t>
+          <t>packages/contracts/src/authz.ts (pure rules), apps/api/src/common/access.ts (AccessContext), org.guard.ts; tables organisation_membership / practice_membership / company_membership; tests: packages/contracts/src/authz.test.ts (22), tests/api/hierarchy.test.ts (25), tests/db/hierarchy.test.ts (16), tests/api/permissions.test.ts (matrix for 8 system roles x 32 probes), tests/unit/architecture.test.ts (central-authoriser rules)</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -7172,6 +8797,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -7219,6 +8849,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -7266,6 +8901,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -7313,9 +8953,34 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>M-L</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>V7 (client portal / billing)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I145"/>
+  <autoFilter ref="A1:N145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7326,7 +8991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -7352,7 +9017,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -7362,7 +9027,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -7372,7 +9037,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -7424,7 +9089,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -7434,7 +9099,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -7444,7 +9109,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -7460,10 +9125,86 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Open rows by recommendation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE V1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Verified code commit</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>a57ebb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CI run</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37901071296</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Generated</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
@@ -7480,7 +9221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7536,29 +9277,29 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>MAN-XVER-03</t>
+          <t>MAN-DOD-05</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>High — Manifest mandates flags for incomplete functionality; V1–V12 will ship incomplete modules, new tax rules and HMRC endpoints behind flags (Cross-Platform §9).</t>
+          <t>High — Definition of Done requires usable UI workflows; V0 foundations are API-only.</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Build flag service (env defaults + per-organisation overrides, audited, cached) before V1 (remediation R4)</t>
+          <t>Build V0 admin UI slices (R5); at minimum documents, tasks, notifications, members, audit</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>MAN-DOD-05</t>
+          <t>MAN-DOD-08</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -7568,19 +9309,19 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>High — Definition of Done requires usable UI workflows; V0 foundations are API-only.</t>
+          <t>High — see OBS rows.</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Build V0 admin UI slices (R5); at minimum documents, tasks, notifications, members, audit</t>
+          <t>R3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>MAN-DOD-08</t>
+          <t>V0-6.1</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -7590,19 +9331,19 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>High — see OBS rows.</t>
+          <t>High — see MAN-TECH-09; production ClamAV is not provisioned (REV-08).</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>Real-S3 run + ClamAV service in Terraform</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>V0-3.1</t>
+          <t>V0-S6</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -7612,41 +9353,41 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>High — V1 (VAT, currency, periods), V3 (Companies House) and V4 (CT/UTR) all need these attributes on the company record.</t>
+          <t>High — see MAN-TECH-09.</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Extend company profile (R1)</t>
+          <t>Real S3 validation (R8)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>V0-3.2</t>
+          <t>V0-S7</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>High — V1 blocker (Customers, Suppliers, Sales, Purchases).</t>
+          <t>High — documented ≠ recoverable. Documents (the evidence base) have versioning/Object Lock but no DR copy.</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Build contacts module (R1)</t>
+          <t>Add S3 replication/backup for DR, run and record a restore drill in staging (R8)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>V0-3.3</t>
+          <t>REV-04</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -7656,41 +9397,41 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>High — needed by contacts, companies, invoices (V1) and filings (V3).</t>
+          <t>High — real-S3 validation has never been performed.</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Build addresses (R1)</t>
+          <t>Staging run with INFRA_ENFORCES_SIGNATURES=1 (R8)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>V0-3.4</t>
+          <t>REV-05</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>High — V3 (Companies House) and V7 (KYC/AML, beneficial owners) depend on officers.</t>
+          <t>High — plan/apply failures (quotas, IAM, KMS policy, name collisions, SES) are likely on first apply.</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Build officers/PSC model (R1)</t>
+          <t>terraform plan in staging, apply, destroy/recreate cycle (R8)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>V0-3.5</t>
+          <t>REV-08</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -7700,232 +9441,3520 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>High — V1 posting validates currency; multi-currency design must exist first.</t>
+          <t>High — in production every upload would fail scanning and stay in SCANNING (fails closed, but the feature is unusable).</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Add global reference table + seed + company base currency (R1)</t>
+          <t>Add ClamAV ECS service (+EFS signature cache or sidecar), service discovery, CLAMAV_HOST env, health alarm (R0)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Specification reference</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Expected behaviour</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Current status</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Risk and impact</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Blocks V1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Blocks production</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Recommended action</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Proposed milestone</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Scope change needing approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>V0-4.7</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>V0 §4</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Must support: SLA/deadline</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Medium — compliance calendar (V7) and escalation need deadlines.</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE V1</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Yes (recommended)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Add `due_at` (and optional SLA hours per definition) to workflow instances, overdue filter, `workflows_overdue` gauge and a one-time overdue notification to the assignee (same sweeper pattern as task reminders). Additive migration, no behaviour change for existing workflows.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>A listed V0 'must support'. V1 approvals will run on this engine, and the compliance calendar (V7) needs deadlines; adding it later means migrating live workflow data. Cheap now.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>None (workflow engine exists)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Pre-V1 gate</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Proposal S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>V0-7.3</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>V0 §7</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Future SMS/WhatsApp adapters</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Low–Medium — retrofitting channels later touches every notifier.</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE V1</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Yes (recommended)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Introduce a NotificationChannel port (in-app, e-mail implemented; SMS/WhatsApp as disabled, documented stubs), a channel registry and per-user channel preferences; route NotificationService through it. Today: two unrelated code paths and five call sites.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Every V1+ notifier would otherwise be written against the two separate paths and have to be migrated; the call-site count only grows.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>S-M (3 d)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Pre-V1 gate</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Proposal S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>V0-9.4</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>V0 Core Tables + Tests</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>integration_jobs; failed integration retry</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Medium — a listed V0 test is only covered generically.</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE V1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Yes (recommended)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Add the listed V0 test: an integration call that fails transiently, is retried with backoff and then succeeds (flaky adapter in the test registry). Record in an ADR that `job_record` (now with company and trace ids) is the integration job table, not a separate `integration_jobs`.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>A listed V0 test covered only generically; V1 bank-feed and Xero integrations will rely on this behaviour.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>S (1 d)</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Injectable test adapter</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Pre-V1 gate</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Proposal S6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>V0-S8</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>V0 Security</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Retention policies</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Medium — unbounded table growth; UK GDPR storage-limitation and statutory record retention both need explicit policy.</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE V1</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Partly: classification only</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Split: (a) before V1 - a retention policy table and per-category retention years (document types, audit, job/outbox records) so ledger data created by V1 is classified from day one; (b) before production - scheduled purge jobs for operational tables (job_record, idempotency_record, expired sessions/tokens, notifications) and erasure-vs-retention rules. Outbox cleanup, legal hold and evidence retention dates already exist.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Statutory retention (six years for company records) applies to V1 data from its first row; back-filling classification afterwards is costly and error-prone.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>L (7-8 d), split S + M/L</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Document types (done), V0-8.3 decision</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Pre-V1 gate (policy + classification), Tranche B (parallel with V1, before first production release) (purge jobs)</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Proposal S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>V0-TEST-6</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>V0 Tests</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Failed integration retry</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE V1</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Yes (recommended)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Delivered together with V0-9.4.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Same requirement.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Included in V0-9.4</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>V0-9.4</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Pre-V1 gate</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Proposal S6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>XP-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Platform §10</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Configurable data retention by category</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE V1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Partly (same split as V0-S8)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Delivered together with V0-S8: configurable retention by category (policy table + purge).</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Same requirement viewed from the cross-platform specification.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Included in V0-S8</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>V0-S8</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Pre-V1 gate / Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Proposal S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MAN-TECH-09</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Manifest › Shared Technical Contract</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Object storage: encrypted document/object storage</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>High — encryption-at-rest, presigned-URL signature enforcement, KMS key policy, Object Lock and CORS are unverified on real S3. moto does not validate signatures.</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Run `pnpm test:infra` against a real staging bucket with signature enforcement on; verify SSE-KMS, key policy, CORS and Object Lock.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Only moto (protocol emulation) has been used.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d)</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Staging AWS account and bucket</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>MAN-TECH-11</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Manifest › Shared Technical Contract</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Observability: structured logs, metrics, tracing and audit events</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Medium - tracing spans, dashboards and SLOs are not part of V0 minimum</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Spans, dashboards and SLOs (see OBS-04, XP-12).</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Logs, metrics, access logs and audit events are delivered; tracing spans are not.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Included in OBS-04 + dashboards (S)</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>OBS-04</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MAN-DOD-05</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Manifest › Definition of Done</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>UI workflows are usable</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>High — Definition of Done requires usable UI workflows; V0 foundations are API-only.</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Decision needed</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Build the V0 UI slices (members/invitations, documents with folders and visibility, tasks, workflows, notifications, AI proposals, audit log, feature flags) with axe checks. Option A (recommended): proceed with V1 API-first and deliver V0 slices in parallel under feature flags. Option B: hold V1 until the slices exist.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>The Manifest's definition of done requires usable UI workflows. Everything V0 provides is reachable through the API only today (the UI covers authentication, security settings and companies).</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>XL (3-4 w for documents, tasks, workflows, notifications, members, integrations, AI proposals, audit)</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>API is complete for all of them; design system</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Needs your decision (S5)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>V0-3.9</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>MAN-DOD-08</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Manifest › Definition of Done</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Observability is present</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>High — see OBS rows.</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Closes with OBS-04 and OBS-05 (staging game-day).</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Same as MAN-TECH-11.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Included in OBS-04/OBS-05</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>OBS-04, OBS-05</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>V0-6.1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>V0 §6</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>High — see MAN-TECH-09; production ClamAV is not provisioned (REV-08).</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Real-S3 run plus ClamAV service in AWS.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Upload pipeline verified against emulation and a real clamd only.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>S + REV-08</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>REV-08, MAN-TECH-09</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>V0-6.10</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>V0 §6</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Immutable filing evidence</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Medium - application and database cannot alter locked evidence, but a privileged operator with bucket access could still delete the stored object until Object Lock is verified in AWS</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Verify S3 Object Lock in COMPLIANCE mode (the Terraform default is GOVERNANCE 30 days) for evidence versions; decide the retention default for locked evidence. The database already refuses every change to locked evidence.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Application and database immutability are proven; object-level immutability is not.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>S (1 d)</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>First Terraform apply</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>V0-7.1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>V0 §7</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Medium — deliverability/sandbox/DKIM/bounce handling untested; no bounce/complaint handling.</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Exercise the SES adapter in staging (sandbox exit, DKIM, bounce/complaint handling with suppression).</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Only file/memory drivers have been exercised.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d)</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>SES domain/DKIM in the account</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>V0-8.3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>V0 §8</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>IP/device metadata where lawful</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Low — GDPR documentation gap.</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Document the lawful basis and retention period for IP address and user agent in the audit trail (the switch `AUDIT_CAPTURE_DEVICE_METADATA` exists and works); add to the privacy notice and the record of processing.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>The control exists; the legal determination and its documentation are the controller's and cannot be made by engineering.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>S (1 d) + legal input</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Retention policy decision (V0-S8)</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Needs your / DPO decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>V0-S1</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>V0 Security</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Encryption in transit</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Medium — unverified until deployed; internal hops unencrypted (acceptable for many baselines, not all).</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Verify TLS at the ALB, `rediss://`, `sslmode=require` and decide whether web-&gt;api traffic inside the VPC needs TLS.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Application-level controls (HSTS, secure cookies, config validation) are tested; infrastructure is not deployed.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>S (1-2 d)</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>First apply</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>V0-S2</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>V0 Security</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Encrypted sensitive data at rest</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Medium — application-level encryption verified; infrastructure encryption unverified. Field-key rotation procedure is documented, not implemented.</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Verify RDS, S3 and log encryption with the intended KMS keys; document field-key rotation.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Field-level encryption is tested; infrastructure encryption is only declared.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>S (1 d)</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>First apply</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>V0-S4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>V0 Security</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Least privilege</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Low–Medium — IAM unreviewed in a real account.</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Review IAM in a real account; use separate database credentials for API and worker; enable `pgaudit`; add connection-level alerting. (Database-level least privilege - append-only privileges, role owns nothing - is tested.)</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>The database trusts the application to assert tenant and user for row-level security; arbitrary SQL execution as the runtime role would defeat it. No raw SQL from strings exists (architecture test).</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>M (3 d)</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>First apply</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>V0-S6</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>V0 Security</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Secure object storage</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>High — see MAN-TECH-09.</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>See MAN-TECH-09.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Same.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Included in MAN-TECH-09</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>MAN-TECH-09</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>V0-S7</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>V0 Security</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Backup and disaster recovery</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>High — documented ≠ recoverable. Documents (the evidence base) have versioning/Object Lock but no DR copy.</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Include S3 in AWS Backup / replication, back up Redis if queues must survive, drill a full restore.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>RDS PITR and daily backups are configured; documents (the evidence base) have versioning and Object Lock but no DR copy.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>M (3-4 d)</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>First apply</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>XP-11</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Platform §11</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility (WCAG-aligned, keyboard, contrast)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Medium — unverified compliance; legal exposure for public-facing client portal later.</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Add automated accessibility checks (axe) to the e2e suite for every UI slice; keyboard and contrast review.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Cannot be verified without the UI; legal exposure grows with the client portal (V7).</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>M (with the UI slices)</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>MAN-DOD-05</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>With S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>XP-12</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Platform §12</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Heavy operations async with visible progress</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Medium — 'feels immediate' is untested.</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Define SLOs, add k6 smoke/load tests for the heavy paths (upload, import/export, report), expose job progress in the UI.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>'Feels immediate' is untested; async behaviour and progress are implemented and tested.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>M (4 d)</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Staging environment, SLO definitions</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (already planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>OBS-04</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Manifest › Observability</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Distributed tracing</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>High — period generation, V2 accounts and V3/V4 deadlines derive from the year-end.</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Add `year_end_month/day` (+ first period rules) to company profile (R1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>V0-6.1</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>OpenTelemetry SDK + ADOT collector replacing the metrics renderers' transport; spans for HTTP, database, queue and job execution. Trace-id propagation API -&gt; job -&gt; worker already exists.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Correlation ids, trace ids, access logs and metrics cover incident triage; spans add latency breakdown.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>M (4 d)</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>ADOT collector in ECS (Terraform)</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (already planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>OBS-05</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Manifest › Observability</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Alerting on DLQ, failed outbox, auth attacks, readiness</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>High — see MAN-TECH-09; production ClamAV is not provisioned (REV-08).</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Real-S3 run + ClamAV service in Terraform</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>V0-8.2</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Medium - defined and validated, but never applied: delivery of alarms to a real inbox and EMF extraction are unproven</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Apply the alarms in staging, confirm EMF extraction and e-mail delivery, run a game-day (stop the worker, fill the DLQ, fail an outbox event).</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Alarms are defined and validated by terraform validate and a drift-guard test but have never run in a real account.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d) in staging</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>First Terraform apply (REV-05)</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>REV-04</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Review request #3</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Moto-based S3 vs real AWS S3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>High — accountant-grade audit trail needs field-level change history (esp. V1 master data, V4 tax).</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Add before/after (redacted) to audit API for update paths (R2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>V0-S6</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>High — real-S3 validation has never been performed.</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Same run as MAN-TECH-09.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Signature enforcement, expiry and KMS are not validated by moto.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d)</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Staging AWS account</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>REV-05</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Review request #4</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Terraform validation vs AWS deployment</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>High — see MAN-TECH-09.</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Real S3 validation (R8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>V0-S7</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>High — plan/apply failures (quotas, IAM, KMS policy, name collisions, SES) are likely on first apply.</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>`terraform plan`/`apply` in staging, fix first-apply failures (quotas, IAM, KMS policy, names, SES), destroy/recreate once. CI proves only fmt/init/validate.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Validation checks syntax, types and references only.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>M (3-4 d)</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>AWS account, state backend</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>REV-07</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Web ↔ API deployment configuration</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>High — documented ≠ recoverable. Documents (the evidence base) have versioning/Object Lock but no DR copy.</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Add S3 replication/backup for DR, run and record a restore drill in staging (R8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>XP-09</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Medium — staging/other envs need a rebuilt image or will call prod's DNS name.</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Resolve the API URL at runtime (or build per environment) instead of baking `API_INTERNAL_URL` into the web image.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Other environments would call the production DNS name.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>S (1 d)</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Web build</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>REV-08</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>ClamAV in AWS</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>REV-04</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>High — in production every upload would fail scanning and stay in SCANNING (fails closed, but the feature is unusable).</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Yes (hard blocker)</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Provision ClamAV (ECS service with the official image, private service discovery name, `CLAMAV_HOST` for api and worker, signature-update egress).</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Production configuration demands the clamav driver, but nothing in Terraform provisions it: every upload would stay SCANNING (fails closed).</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>M (3 d)</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Terraform: ECS service + service discovery for clamd</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>REV-09</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Redis configuration for BullMQ</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>High — real-S3 validation has never been performed.</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Staging run with INFRA_ENFORCES_SIGNATURES=1 (R8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>REV-05</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Replace `default.redis7` with a parameter group setting `maxmemory-policy noeviction` (required by BullMQ) and add the Redis eviction alarm.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Default eviction can drop queued jobs under memory pressure.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>S (0.5 d)</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>REV-10</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Review request #6</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Migrations and recovery documentation</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>High — plan/apply failures (quotas, IAM, KMS policy, name collisions, SES) are likely on first apply.</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>terraform plan in staging, apply, destroy/recreate cycle (R8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>REV-06</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Rehearse a failed migration and a restore from the latest snapshot in staging; record timings in the runbook.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Procedures are documented and the migration path is tested from scratch and on populated databases, but no restore has been drilled.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d)</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Staging DB snapshot</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Production gate (Tranche C, real AWS)</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Production gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>REV-11</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Database connection management</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Set explicit pool sizes per service, consider RDS Proxy, size `rds_connections` alarm from measurement.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Default pool sizes times api and worker tasks could exhaust connections under load.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>S-M (2-3 d)</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Load test (XP-12)</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>REV-13</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>V6 §Human-in-the-Loop / Explainability / Privacy (forward)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>AI state vocabulary (V6: SUGGESTED -&gt; REVIEWED -&gt; ACCEPTED/REJECTED), explainability (prompt version, evidence, confidence) and privacy gate</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Medium - privacy gate missing (low until real providers are enabled)</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>MUST FIX BEFORE PRODUCTION</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Yes (before any external AI provider)</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Per-organisation AI data-processing consent record (who accepted what, when) checked before any external provider call. Today AI and OCR are off by default per organisation (`ai.beta`, `documents.ocr`) and no external provider exists.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Privacy gate for external AI; not needed while only fake providers exist.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>S (2 d)</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Legal input on data processing</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release)</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Needs your decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>V0-1.9</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>V0 §1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>device/session management</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Medium — spec asks for device management; security teams expect new-device notification and admin kill-switch.</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Recommended (new-device alert)</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Add a stable device identity (cookie-bound), new-device e-mail alert, per-device revoke and an admin 'revoke all sessions for a user' kill-switch. Sessions are already listed and revocable, MFA exists, sessions are server-side and revoked on password reset.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Hardening, not a V1 dependency. Becomes important when external client users arrive (V7). Recommended before production for staff accounts.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>M (4 d)</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Notification channel port (V0-7.3) for the new-device alert</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Tranche B (parallel with V1, before first production release) / V7 client portal</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Proposal S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>V0-9.2</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>V0 §9</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Adapters for HMRC, Companies House, banks, Xero, QuickBooks, FreeAgent, Stripe, Shopify, payroll, payment providers</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Low — appropriate for V0 'foundation'.</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Named adapters are delivered by the versions that need them, through the existing adapter interface and registry (the only place providers are registered). The V0 deliverable - the interface, credential encryption, host allow-list, mock adapter, retries - is complete.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>The V0 specification asks for an 'adapter interface'; the named providers are the work of later versions.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>n/a for V0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>V3 / V4 / V5 / V11</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>V3 (Companies House), V4/V5 (HMRC), V11 (banks, Xero, QuickBooks, FreeAgent, Stripe, Shopify, payroll)</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>V0-10.3</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>V0 §10</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Embedding/Search provider</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>High — supply-chain controls absent; findings are low-exploitability (build-time) but would fail an audit gate.</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Pin patched versions via pnpm overrides/upgrade Next &amp; Prisma; restore `pnpm audit --audit-level=high`, add CodeQL, secret scanning, image scan (R0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>REV-08</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>High — in production every upload would fail scanning and stay in SCANNING (fails closed, but the feature is unusable).</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Add ClamAV ECS service (+EFS signature cache or sidecar), service discovery, CLAMAV_HOST env, health alarm (R0)</t>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Medium — universal search/AI retrieval (Cross-Platform §2, V10).</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Add EmbeddingProvider and SearchProvider ports with deterministic fakes (no storage, no endpoints), beside the existing AI and OCR ports.</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Pure abstraction with no V1 consumer; first needed by V6/V10 (universal search, retrieval). Doing it now is cheap and would let V0 §10 be marked complete.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>S (1-2 d) if done now</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>V6 (OCR/AI) - or the Pre-V1 gate if you want V0 spec-complete</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Proposal S7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>XP-02</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Platform §2</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Universal search</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Medium (design) — search technology (Postgres FTS vs OpenSearch) and per-tenant index design should be decided before V1 data models.</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Design decision</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Decide search technology (Postgres FTS vs OpenSearch) and per-tenant index design before V1 reporting.</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Design decision, no V0 code.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>M design</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Document extraction (delivered)</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>V1 design / V10</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>XP-03</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Platform §3–5</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Exception-first UX, command centre, materiality engine</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Low — materiality settings store should be designed with company profile (R1).</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Materiality settings store designed with the company profile in V1/V2.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Product features of later versions.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>V1+</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>V1+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>REV-12</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Container images</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Low–Medium — larger attack surface/size.</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Multi-stage prune of dev dependencies and sources from runtime images (`pnpm deploy`). The Trivy HIGH/CRITICAL gate, OS upgrade and npm removal are done.</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Size and surface reduction; the scan gate is passing on all four images.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>S (1-2 d)</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>CHG-DEF1</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Deliberately not built (scope)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Cross-organisation engagement (a client business with its own organisation instructing a practice), billing/seat counting, UI for practices and grants, audit/job/integration company dimension</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Medium - needed before client-portal/billing work</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>DEFER TO A LATER VERSION</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Explicit cross-organisation engagement grant when a client business needs its own organisation.</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Deliberately not built (documented in the design).</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>M-L</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Hierarchy design section 8</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>V7 (client portal / billing)</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>MAN-CTRL-01</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Manifest › Non-Negotiable Accounting Controls 1–9</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>PostingService, immutable posted journals, reversals, balanced entries, source/actor/timestamp metadata, traceability, drill-down, period states, effective-dated rules</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>None for V0. Pre-V1 design risk: a dedicated posting DB role + trigger pattern (like forbid_mutation) must be designed before V1 coding.</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Design input</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Accounting controls are V1 deliverables; V0 supplies the primitives (append-only pattern, central authoriser, outbox).</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Not a V0 requirement.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>MAN-DIFF</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Manifest › Strategic Differentiators</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>AI bookkeeping, working papers, CFO forecasting, etc.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Differentiators are later versions.</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Not a V0 requirement.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>V6-V12</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>V6-V12</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>V0-1.5</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>V0 §1 + Core Tables</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>permissions (entity/table)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Low — functionally complete; a table would only help dynamic permission registration by V8–V12 plug-ins.</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Accept the deviation: the permission catalogue lives in code (typed, test-synchronised with the database role seed) and `role.permissions` stores grants. A `permissions` table would create a second source of truth.</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Functionally complete and tested (permission matrix: 8 roles x 32 probes); only dynamic plug-in registration (V8-V12) would benefit.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Needs your acceptance</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>V0-T2</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>V0 Core Tables</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>permissions, contacts, integration_jobs, ai_requests</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>See linked rows</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Accept the deviations: `contacts` now exists; `permissions` is the code catalogue (see V0-1.5); `integration_jobs` is `job_record` (queue `integrations`, with company and trace ids); `ai_requests` is `ai_run`.</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Equivalent function, singular snake_case naming approved under D5.</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Needs your acceptance</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>XP-01</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Platform §1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Universal drill-down</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>None for V0 (see XP-06 for the foundation)</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>The evidence graph (XP-06, delivered) is the V0 foundation for drill-down.</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>UI/report feature of later versions.</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>V1+</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>V1+</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>XP-13</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Platform §13–14</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Mobile-first portal; product design language</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>None for V0</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Mobile-first portal is V7.</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Not a V0 requirement.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N45"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Proposed milestone</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Workflow deadlines / SLA (V0-4.7)</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>S (2 d)</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Before V1</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Additive; migration + sweeper reusing the task-reminder pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Notification channel port + preferences (V0-7.3)</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>S-M (3 d)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Before V1</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Refactors NotificationService behind a port; five call sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Device identity, new-device alert, admin session kill-switch (V0-1.9)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>M (4 d)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Tranche B / V7</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Needs S2 for the alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Retention: (a) policy table + per-category classification; (b) purge jobs + erasure rules (V0-S8, XP-10)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>S-M (2-3 d) + M-L (5 d)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>(a) before V1, (b) before production</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Needs your decision on retention periods and the lawful basis (V0-8.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>UI slices for V0 foundations (MAN-DOD-05, XP-11)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>XL (3-4 w)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Tranche B, in parallel with V1 under feature flags - or hold V1</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Needs your decision: API-first V1 or UI-first</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Integration retry test + ADR 'job_record is the integration job table' (V0-9.4, V0-TEST-6)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>S (1 d)</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Before V1</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Test infrastructure only</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>EmbeddingProvider / SearchProvider ports with fakes (V0-10.3)</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>S (1-2 d)</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Optional now; otherwise V6</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Pure abstraction; lets V0 section 10 be marked complete</t>
         </is>
       </c>
     </row>

--- a/docs/architecture/v0-compliance-matrix.xlsx
+++ b/docs/architecture/v0-compliance-matrix.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matrix'!$A$1:$N$145</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Decision register'!$A$1:$N$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Decision register'!$A$1:$N$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -70,11 +70,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -119,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -150,9 +145,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1521,7 +1513,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16 migrations in packages/db/prisma/migrations (baseline through 20260104000900), additive or data-preserving (one forward-only enum value, documented); applied from scratch with the production script in CI (job 'migrations-from-scratch'), as a non-superuser owner, and onto populated databases (data preserved, FK validation under forced RLS covered): tests/db/upgrade.test.ts (6), tests/unit/migrations.test.ts (18); docs/runbooks/migrations.md</t>
+          <t>16 migrations in packages/db/prisma/migrations (baseline through 20260104000900), additive or data-preserving (one forward-only enum value, documented); applied from scratch with the production script in CI (job 'migrations-from-scratch'), as a non-superuser owner, and onto populated databases (data preserved, FK validation under forced RLS covered): tests/db/upgrade.test.ts (6), tests/unit/migrations.test.ts (21); docs/runbooks/migrations.md</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1677,7 +1669,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Audit events exist for authentication, organisation, company, period, document, folder, task, review, evidence, feature-flag, integration and workflow actions, written in the business transaction, append-only by privilege AND trigger. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (21) (append-only privileges), tests/db/rls.test.ts (27)</t>
+          <t>Audit events exist for authentication, organisation, company, period, document, folder, task, review, evidence, feature-flag, integration and workflow actions, written in the business transaction, append-only by privilege AND trigger. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (23) (append-only privileges), tests/db/rls.test.ts (27)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1801,7 +1793,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Verified commit a57ebb3: CI run https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37901071296 - all 9 jobs green (build/lint/typecheck/unit/integration/e2e; real S3 protocol + real ClamAV; dependency audit + secret scan; migrations from scratch; terraform fmt/init/validate; images api, worker, web, migrate with Trivy) plus CodeQL; clean-clone: fresh git clone, pnpm install --frozen-lockfile, build, typecheck, lint, 956/956 unit+integration tests (51 files), 4/4 real-browser e2e tests, OpenAPI regeneration without drift. Local: 956 unit+integration tests passed (51 files), 0 failed, 0 skipped.</t>
+          <t>Verified commit 3b754e7: CI run https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37913579987 - all 9 jobs green (build/lint/typecheck/unit/integration/e2e; real S3 protocol + real ClamAV; dependency audit + secret scan; migrations from scratch; terraform fmt/init/validate; images api, worker, web, migrate with Trivy) plus CodeQL; clean-clone: fresh git clone, pnpm install --frozen-lockfile, build, typecheck, lint, 1034/1034 unit+integration tests (59 files), 4/4 real-browser e2e tests, OpenAPI regeneration without drift. Local: 1034 unit+integration tests passed (59 files), 0 failed, 0 skipped.</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -2817,7 +2809,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>company profile: incorporation date, financial year-end, base currency, country, tax jurisdiction, practice, legal form, status; PATCH /companies/{id} validated against reference data and audited with before/after; addresses via address table; GET /companies/{id}/periods/next derives the next period. VAT/UTR/PAYE references and Companies House status are owned by V3/V4/V5 with their own lawful basis. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+          <t>company profile: incorporation date, financial year-end, base currency, country, tax jurisdiction, practice, legal form, status; PATCH /companies/{id} validated against reference data and audited with before/after; addresses via address table; GET /companies/{id}/periods/next derives the next period. VAT/UTR/PAYE references and Companies House status are owned by V3/V4/V5 with their own lawful basis. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (99)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2869,7 +2861,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>contact (PERSON/ORGANISATION, organisation-level or company-level, archive/restore, labels, search), contact:read/manage COMPANY-scope permissions. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+          <t>contact (PERSON/ORGANISATION, organisation-level or company-level, archive/restore, labels, search), contact:read/manage COMPANY-scope permissions. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (99)</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2921,7 +2913,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>address owned by exactly one company or contact (DB check), kinds, one primary per owner+kind (partial unique index), UK postcode validated in API and database. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+          <t>address owned by exactly one company or contact (DB check), kinds, one primary per owner+kind (partial unique index), UK postcode validated in API and database. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (99)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2973,7 +2965,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>company_officer: contact appointed to an office with appointed/resigned dates, history kept, contact must be organisation-level or the same company's (trigger). Data-minimised (no date of birth or nationality until V3). migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+          <t>company_officer: contact appointed to an office with appointed/resigned dates, history kept, contact must be organisation-level or the same company's (trigger). Data-minimised (no date of birth or nationality until V3). migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (99)</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -3025,7 +3017,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>currency REFERENCE table seeded from system ISO 4217 data (159 transactional codes), company base_currency FK (default GBP), SELECT-only for the runtime role. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+          <t>currency REFERENCE table seeded from system ISO 4217 data (159 transactional codes), company base_currency FK (default GBP), SELECT-only for the runtime role. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (99)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -3077,7 +3069,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>country REFERENCE table seeded from ISO 3166-1 (249), alpha-2/alpha-3/numeric, company country FK. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+          <t>country REFERENCE table seeded from ISO 3166-1 (249), alpha-2/alpha-3/numeric, company country FK. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (99)</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -3129,7 +3121,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>tax_jurisdiction: effective-dated (valid_from/valid_to, exclusion constraint so a code never overlaps itself), GB-HMRC and IE-REV seeded, `?asOf=` query, company tax_jurisdiction_code FK. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+          <t>tax_jurisdiction: effective-dated (valid_from/valid_to, exclusion constraint so a code never overlaps itself), GB-HMRC and IE-REV seeded, `?asOf=` query, company tax_jurisdiction_code FK. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (99)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -3233,7 +3225,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>company year_end_month/day (29 Feb = last day of February; CHECK with NOT NULL guards), pure nextAccountingPeriod() (no gap, no overlap, leap years), GET /companies/{id}/periods/next. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (93)</t>
+          <t>company year_end_month/day (29 Feb = last day of February; CHECK with NOT NULL guards), pure nextAccountingPeriod() (no gap, no overlap, leap years), GET /companies/{id}/periods/next. migration 20260104000300 (REFERENCE tables currency [159 ISO 4217], country [249 ISO 3166-1], effective-dated tax_jurisdiction [exclusion constraint]; tenant tables contact, address, company_officer with composite FKs and forced RLS; company profile columns), apps/api/src/master-data/*, apps/api/src/companies/companies.service.ts, packages/contracts/src/financial-year.ts. Tests: tests/api/master-data.test.ts (22), tests/db/master-data.test.ts (13), packages/contracts/src/financial-year.test.ts (9), tests/db/classification.test.ts (99)</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -3597,59 +3589,39 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>No due date/SLA fields; no overdue detection.</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+          <t>workflow_instance.due_at, overdue_notified_at and failure accounting (migration 20260105000000); optional slaHours per definition (default deadline at start, none shipped); POST /workflows/{id}/due-date (workflow:manage for the company, optimistic version, set/move/clear recorded in history, audit before/after and outbox); GET /workflows?overdue=; computed `overdue` flag; WorkflowOverdueSweeper (system-context listing, one tenant transaction per instance, FOR UPDATE SKIP LOCKED, notification + marker atomic = exactly once, back-off, abandonment audited); gauge workflows_overdue; ADR-37; v0-tranche-a.md 9.2. Tests: tests/platform/workflow-overdue.test.ts (10), tests/api/workflow-deadlines.test.ts (9), tests/api/observability.test.ts (12)</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Medium — compliance calendar (V7) and escalation need deadlines.</t>
+          <t>Low - resolved (ADR-37). A reopened instance does not re-arm the notification; set a new deadline to do that (documented)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Add due_at + scheduled overdue-detection job emitting events/notifications (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Job + notification tests</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>MUST FIX BEFORE V1</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Yes (recommended)</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>S (2 d)</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>Pre-V1 gate</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4769,27 +4741,27 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>No channel abstraction: NotificationService.notify (in-app) and email() are separate code paths; no channel registry/preferences.</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>NotificationChannel port + registry (packages/platform/src/notification-channels.ts): in_app inline, e-mail planned in the business transaction (notification_delivery) and executed by NotificationDeliverySweeper through the existing email.send job keyed by the delivery id; SMS and WhatsApp registered as unavailable stubs (cannot be enabled by configuration or preference, fail loudly if reached); per-user opt-in preferences (GET/PUT /notifications/preferences, e-mail default off, in-app mandatory, audited); content-free e-mail; NotificationService routes every caller through the port. Migration 20260105000100; ADR-38. Tests: tests/platform/notification-channels.test.ts (18), tests/api/notification-preferences.test.ts (7), tests/db/privileges.test.ts (23)</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Low–Medium — retrofitting channels later touches every notifier.</t>
+          <t>Low - resolved. No SMS/WhatsApp provider exists by design (stubs); a real e-mail provider (SES) is a production-gate item</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Introduce NotificationChannel port + registry + per-user preferences (R2)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Fake SMS channel test</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4797,31 +4769,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>MUST FIX BEFORE V1</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>Yes (recommended)</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>S-M (3 d)</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>Pre-V1 gate</t>
-        </is>
-      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4893,7 +4845,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Structured before/after (changed fields only, redacted, size-capped) on company, task, document, contact, officer, membership, feature-flag and workflow actions. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (21) (append-only privileges), tests/db/rls.test.ts (27)</t>
+          <t>Structured before/after (changed fields only, redacted, size-capped) on company, task, document, contact, officer, membership, feature-flag and workflow actions. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (23) (append-only privileges), tests/db/rls.test.ts (27)</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -5017,7 +4969,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Optional reason on audited actions (member removal, archive, feature-flag change, document edit); mandatory for decisions: task returns, evidence locks and evidence-link revocation. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (21) (append-only privileges), tests/db/rls.test.ts (27)</t>
+          <t>Optional reason on audited actions (member removal, archive, feature-flag change, document edit); mandatory for decisions: task returns, evidence locks and evidence-link revocation. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (23) (append-only privileges), tests/db/rls.test.ts (27)</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -5069,7 +5021,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>source_workflow_id recorded when the action is part of a workflow (workflow transitions, AI proposal application); correlation id on every event. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (21) (append-only privileges), tests/db/rls.test.ts (27)</t>
+          <t>source_workflow_id recorded when the action is part of a workflow (workflow transitions, AI proposal application); correlation id on every event. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (23) (append-only privileges), tests/db/rls.test.ts (27)</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -5297,59 +5249,39 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>No `integration_jobs` table; calls run as generic `job_record` (queue `integrations`). Generic retry/backoff/DLQ tested; **no test of an integration call that fails transiently then succeeds**, and job_record has no company_id.</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>Decision (ADR-36, approved scope S6): job_record is the integration job table - status, attempts, exponential backoff, dead-lettering, encrypted sensitive payloads, idempotency, operator retry, organisation/company/trace/correlation ids (migration 20260104000900); no separate integration_jobs. Test: an integration.execute call through the real worker fails transiently (mock provider `flaky` operation), is retried with backoff (&gt;= 15 s over three attempts) and succeeds; client errors fail at once; credentials never reach the record. tests/jobs/integration-retry.test.ts (5), tests/jobs/jobs.test.ts (14)</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Medium — a listed V0 test is only covered generically.</t>
+          <t>Low - resolved. The table name differs from the specification by decision (ADR-36); see V0-T2</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Add integration-retry test with flaky adapter; decide table vs job_record (ADR)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>New test in tests/api/foundations.test.ts</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>MUST FIX BEFORE V1</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>Yes (recommended)</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>S (1 d)</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>Pre-V1 gate</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5917,7 +5849,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Forced row-level security on every tenant table (registry == database, classification test), composite (organisation_id, id) foreign keys, tenant context set per transaction, runtime role without BYPASSRLS that owns nothing; tests: tests/db/rls.test.ts (27), tests/db/classification.test.ts (93), tests/api/tenancy.test.ts (21), tests/db/privileges.test.ts (21), tests/unit/architecture.test.ts (16) (no code path bypasses the tenant context). Residual trust boundary documented: the database trusts the application to assert tenant and user</t>
+          <t>Forced row-level security on every tenant table (registry == database, classification test), composite (organisation_id, id) foreign keys, tenant context set per transaction, runtime role without BYPASSRLS that owns nothing; tests: tests/db/rls.test.ts (27), tests/db/classification.test.ts (99), tests/api/tenancy.test.ts (21), tests/db/privileges.test.ts (23), tests/unit/architecture.test.ts (16) (no code path bypasses the tenant context). Residual trust boundary documented: the database trusts the application to assert tenant and user</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -6041,7 +5973,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>gitleaks secret scan in CI (job 'dependency audit + secret scan', green on a57ebb3), .gitleaks.toml, secrets from AWS Secrets Manager (Terraform), `.env.example` has blanks, config validation refuses unsafe production settings (packages/core/src/config.test.ts). Repository push protection is a GitHub setting the repository owner must enable (not verifiable here)</t>
+          <t>gitleaks secret scan in CI (job 'dependency audit + secret scan', green on 3b754e7), .gitleaks.toml, secrets from AWS Secrets Manager (Terraform), `.env.example` has blanks, config validation refuses unsafe production settings (packages/core/src/config.test.ts). Repository push protection is a GitHub setting the repository owner must enable (not verifiable here)</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -6237,7 +6169,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Columns `document.retain_until`, `legal_hold`; legal hold blocks archive (tested); documents never hard-deleted. **No configurable retention policy per category, no enforcement, no purge/cleanup jobs** for job_record, outbox_event, idempotency_record, expired sessions/tokens, notifications.</t>
+          <t>Classification delivered (ADR-39, approved scope S4(a)): retention_category (15 categories, provisional periods with statutory basis) and retention_rule (every document type and every table mapped; a table without a rule fails the build) as REFERENCE data; GET /reference/retention-categories; retainUntil(). Existing: document.retain_until + legal_hold (legal hold blocks archive), filing-evidence lock, outbox cleanup (14 days, equals the classification). NOT delivered: purge/cleanup jobs, erasure-versus-retention rules, enforcement; no period is CONFIRMED (DPO/legal decision open, V0-8.3). Tests: tests/db/retention.test.ts (6), packages/contracts/src/retention.test.ts (10), tests/api/retention.test.ts (2)</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -6247,12 +6179,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Medium — unbounded table growth; UK GDPR storage-limitation and statutory record retention both need explicit policy.</t>
+          <t>Medium - unbounded growth of operational tables until the purge work (S4(b)) exists; UK GDPR storage-limitation needs the confirmed policy</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Retention policy tables + scheduled purge jobs + erasure-vs-retention rules (R6)</t>
+          <t>S4(b), before production and not approved yet: scheduled purge jobs for operational tables and erasure-versus-retention rules, after the DPO/legal decision on periods and lawful basis</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6267,12 +6199,12 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>MUST FIX BEFORE V1</t>
+          <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>Partly: classification only</t>
+          <t>No (classification delivered)</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
@@ -6282,12 +6214,12 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>L (7-8 d), split S + M/L</t>
+          <t>M-L (5 d)</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Pre-V1 gate (policy + classification), Tranche B (parallel with V1, before first production release) (purge jobs)</t>
+          <t>Tranche B (parallel with V1, before first production release) (before first production release)</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6345,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Audit creation asserted across auth, company, document, task, workflow, AI, integration, feature-flag and evidence tests; before/after/reason/source-workflow asserted in the audit framework tests; append-only asserted by privilege matrix and triggers. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (21) (append-only privileges), tests/db/rls.test.ts (27)</t>
+          <t>Audit creation asserted across auth, company, document, task, workflow, AI, integration, feature-flag and evidence tests; before/after/reason/source-workflow asserted in the audit framework tests; append-only asserted by privilege matrix and triggers. packages/platform/src/audit.ts (auditRow: redaction, 16 KB snapshot cap, reason &lt;= 1000; changeSet: only changed fields), audit_event columns company_id / before / after / reason / source_workflow_id (migration 20260104000000; composite company/organisation trigger), audit:read is COMPANY-scoped (ADR-28) so readers see only their companies' events, AUDIT_CAPTURE_DEVICE_METADATA switch for IP/user agent, workflow engine and AI application write source_workflow_id. Tests: tests/api/audit-framework.test.ts (13), tests/api/audit-privacy.test.ts (1), packages/platform/src/audit.test.ts (6), tests/db/privileges.test.ts (23) (append-only privileges), tests/db/rls.test.ts (27)</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -6569,59 +6501,39 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>See V0-9.4 — generic job retry only.</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>Failed integration retry: tests/jobs/integration-retry.test.ts (5) (transient failure -&gt; RETRYING -&gt; success on attempt 3; permanent failures not retried). See V0-9.4.</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low - resolved</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Add specific test</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>New test</t>
+          <t>pnpm test</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>MUST FIX BEFORE V1</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>Yes (recommended)</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="inlineStr">
-        <is>
-          <t>Included in V0-9.4</t>
-        </is>
-      </c>
-      <c r="N107" s="2" t="inlineStr">
-        <is>
-          <t>Pre-V1 gate</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7117,7 +7029,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>See V0-S8.</t>
+          <t>Retention is classified per category (see V0-S8): configurable by migration, not at runtime; periods are PROVISIONAL; nothing is enforced yet.</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -7127,32 +7039,32 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
+          <t>Medium - classification exists, enforcement does not</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>S4(b), before production (see V0-S8)</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>R6</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>MUST FIX BEFORE V1</t>
+          <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>Partly (same split as V0-S8)</t>
+          <t>No (classification delivered)</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -7162,12 +7074,12 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>Included in V0-S8</t>
+          <t>Included in V0-S8 (b)</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>Pre-V1 gate / Tranche B (parallel with V1, before first production release)</t>
+          <t>Tranche B (parallel with V1, before first production release)</t>
         </is>
       </c>
     </row>
@@ -8005,7 +7917,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>CI job 'dependency audit + secret scan' (https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37901071296) runs `pnpm audit --audit-level=high`; local `pnpm audit --prod --audit-level=high`: no known vulnerabilities; pnpm overrides for postcss/deepmerge-ts; Vitest 4; CodeQL workflow (green on the verified commit); gitleaks; dependency-review on pull requests; Dependabot; Trivy HIGH/CRITICAL gate on all four images (green). docs/runbooks/supply-chain.md</t>
+          <t>CI job 'dependency audit + secret scan' (https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37913579987) runs `pnpm audit --audit-level=high`; local `pnpm audit --prod --audit-level=high`: no known vulnerabilities; pnpm overrides for postcss/deepmerge-ts; Vitest 4; CodeQL workflow (green on the verified commit); gitleaks; dependency-review on pull requests; Dependabot; Trivy HIGH/CRITICAL gate on all four images (green). docs/runbooks/supply-chain.md</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -8628,7 +8540,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>SLA/deadline (V0-4.7) still open</t>
+          <t>Workflow deadlines delivered (V0-4.7, ADR-37)</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -9017,7 +8929,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3">
@@ -9027,7 +8939,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -9037,7 +8949,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -9099,7 +9011,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -9109,7 +9021,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -9141,7 +9053,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -9151,7 +9063,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -9182,7 +9094,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>a57ebb3</t>
+          <t>3b754e7</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9106,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37901071296</t>
+          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37913579987</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9555,37 +9467,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>V0-4.7</t>
+          <t>MAN-TECH-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>V0 §4</t>
+          <t>Manifest › Shared Technical Contract</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Must support: SLA/deadline</t>
+          <t>Object storage: encrypted document/object storage</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Medium — compliance calendar (V7) and escalation need deadlines.</t>
+          <t>High — encryption-at-rest, presigned-URL signature enforcement, KMS key policy, Object Lock and CORS are unverified on real S3. moto does not validate signatures.</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>MUST FIX BEFORE V1</t>
+          <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Yes (recommended)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -9595,12 +9507,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Add `due_at` (and optional SLA hours per definition) to workflow instances, overdue filter, `workflows_overdue` gauge and a one-time overdue notification to the assignee (same sweeper pattern as task reminders). Additive migration, no behaviour change for existing workflows.</t>
+          <t>Run `pnpm test:infra` against a real staging bucket with signature enforcement on; verify SSE-KMS, key policy, CORS and Object Lock.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>A listed V0 'must support'. V1 approvals will run on this engine, and the compliance calendar (V7) needs deadlines; adding it later means migrating live workflow data. Cheap now.</t>
+          <t>Only moto (protocol emulation) has been used.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -9610,34 +9522,34 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>None (workflow engine exists)</t>
+          <t>Staging AWS account and bucket</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Pre-V1 gate</t>
+          <t>Production gate (Tranche C, real AWS)</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Proposal S1</t>
+          <t>Production gate</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>V0-7.3</t>
+          <t>MAN-TECH-11</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>V0 §7</t>
+          <t>Manifest › Shared Technical Contract</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Future SMS/WhatsApp adapters</t>
+          <t>Observability: structured logs, metrics, tracing and audit events</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -9647,69 +9559,69 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Low–Medium — retrofitting channels later touches every notifier.</t>
+          <t>Medium - tracing spans, dashboards and SLOs are not part of V0 minimum</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>MUST FIX BEFORE V1</t>
+          <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Yes (recommended)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Introduce a NotificationChannel port (in-app, e-mail implemented; SMS/WhatsApp as disabled, documented stubs), a channel registry and per-user channel preferences; route NotificationService through it. Today: two unrelated code paths and five call sites.</t>
+          <t>Spans, dashboards and SLOs (see OBS-04, XP-12).</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Every V1+ notifier would otherwise be written against the two separate paths and have to be migrated; the call-site count only grows.</t>
+          <t>Logs, metrics, access logs and audit events are delivered; tracing spans are not.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>S-M (3 d)</t>
+          <t>Included in OBS-04 + dashboards (S)</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OBS-04</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Pre-V1 gate</t>
+          <t>Tranche B (parallel with V1, before first production release)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Proposal S2</t>
+          <t>Tranche B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>V0-9.4</t>
+          <t>MAN-DOD-05</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>V0 Core Tables + Tests</t>
+          <t>Manifest › Definition of Done</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>integration_jobs; failed integration retry</t>
+          <t>UI workflows are usable</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9719,69 +9631,69 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Medium — a listed V0 test is only covered generically.</t>
+          <t>High — Definition of Done requires usable UI workflows; V0 foundations are API-only.</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>MUST FIX BEFORE V1</t>
+          <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Yes (recommended)</t>
+          <t>Decision needed</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Add the listed V0 test: an integration call that fails transiently, is retried with backoff and then succeeds (flaky adapter in the test registry). Record in an ADR that `job_record` (now with company and trace ids) is the integration job table, not a separate `integration_jobs`.</t>
+          <t>Build the V0 UI slices (members/invitations, documents with folders and visibility, tasks, workflows, notifications, AI proposals, audit log, feature flags) with axe checks. Option A (recommended): proceed with V1 API-first and deliver V0 slices in parallel under feature flags. Option B: hold V1 until the slices exist.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>A listed V0 test covered only generically; V1 bank-feed and Xero integrations will rely on this behaviour.</t>
+          <t>The Manifest's definition of done requires usable UI workflows. Everything V0 provides is reachable through the API only today (the UI covers authentication, security settings and companies).</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>S (1 d)</t>
+          <t>XL (3-4 w for documents, tasks, workflows, notifications, members, integrations, AI proposals, audit)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Injectable test adapter</t>
+          <t>API is complete for all of them; design system</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Pre-V1 gate</t>
+          <t>Tranche B (parallel with V1, before first production release)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Proposal S6</t>
+          <t>Needs your decision (S5)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>V0-S8</t>
+          <t>MAN-DOD-08</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>V0 Security</t>
+          <t>Manifest › Definition of Done</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Retention policies</t>
+          <t>Observability is present</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -9791,17 +9703,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Medium — unbounded table growth; UK GDPR storage-limitation and statutory record retention both need explicit policy.</t>
+          <t>High — see OBS rows.</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>MUST FIX BEFORE V1</t>
+          <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Partly: classification only</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -9811,49 +9723,49 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Split: (a) before V1 - a retention policy table and per-category retention years (document types, audit, job/outbox records) so ledger data created by V1 is classified from day one; (b) before production - scheduled purge jobs for operational tables (job_record, idempotency_record, expired sessions/tokens, notifications) and erasure-vs-retention rules. Outbox cleanup, legal hold and evidence retention dates already exist.</t>
+          <t>Closes with OBS-04 and OBS-05 (staging game-day).</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Statutory retention (six years for company records) applies to V1 data from its first row; back-filling classification afterwards is costly and error-prone.</t>
+          <t>Same as MAN-TECH-11.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>L (7-8 d), split S + M/L</t>
+          <t>Included in OBS-04/OBS-05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Document types (done), V0-8.3 decision</t>
+          <t>OBS-04, OBS-05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Pre-V1 gate (policy + classification), Tranche B (parallel with V1, before first production release) (purge jobs)</t>
+          <t>Tranche B (parallel with V1, before first production release)</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Proposal S4</t>
+          <t>Tranche B</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>V0-TEST-6</t>
+          <t>V0-6.1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>V0 Tests</t>
+          <t>V0 §6</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Failed integration retry</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -9863,69 +9775,69 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High — see MAN-TECH-09; production ClamAV is not provisioned (REV-08).</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>MUST FIX BEFORE V1</t>
+          <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Yes (recommended)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Delivered together with V0-9.4.</t>
+          <t>Real-S3 run plus ClamAV service in AWS.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Same requirement.</t>
+          <t>Upload pipeline verified against emulation and a real clamd only.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Included in V0-9.4</t>
+          <t>S + REV-08</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>V0-9.4</t>
+          <t>REV-08, MAN-TECH-09</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Pre-V1 gate</t>
+          <t>Production gate (Tranche C, real AWS)</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Proposal S6</t>
+          <t>Production gate</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>XP-10</t>
+          <t>V0-6.10</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Cross-Platform §10</t>
+          <t>V0 §6</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Configurable data retention by category</t>
+          <t>Immutable filing evidence</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -9935,17 +9847,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Medium - application and database cannot alter locked evidence, but a privileged operator with bucket access could still delete the stored object until Object Lock is verified in AWS</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>MUST FIX BEFORE V1</t>
+          <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Partly (same split as V0-S8)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -9955,49 +9867,49 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Delivered together with V0-S8: configurable retention by category (policy table + purge).</t>
+          <t>Verify S3 Object Lock in COMPLIANCE mode (the Terraform default is GOVERNANCE 30 days) for evidence versions; decide the retention default for locked evidence. The database already refuses every change to locked evidence.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Same requirement viewed from the cross-platform specification.</t>
+          <t>Application and database immutability are proven; object-level immutability is not.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Included in V0-S8</t>
+          <t>S (1 d)</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>V0-S8</t>
+          <t>First Terraform apply</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Pre-V1 gate / Tranche B (parallel with V1, before first production release)</t>
+          <t>Production gate (Tranche C, real AWS)</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Proposal S4</t>
+          <t>Production gate</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MAN-TECH-09</t>
+          <t>V0-7.1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Manifest › Shared Technical Contract</t>
+          <t>V0 §7</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Object storage: encrypted document/object storage</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -10007,10 +9919,10 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>High — encryption-at-rest, presigned-URL signature enforcement, KMS key policy, Object Lock and CORS are unverified on real S3. moto does not validate signatures.</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
+          <t>Medium — deliverability/sandbox/DKIM/bounce handling untested; no bounce/complaint handling.</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -10027,12 +9939,12 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Run `pnpm test:infra` against a real staging bucket with signature enforcement on; verify SSE-KMS, key policy, CORS and Object Lock.</t>
+          <t>Exercise the SES adapter in staging (sandbox exit, DKIM, bounce/complaint handling with suppression).</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Only moto (protocol emulation) has been used.</t>
+          <t>Only file/memory drivers have been exercised.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -10042,7 +9954,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Staging AWS account and bucket</t>
+          <t>SES domain/DKIM in the account</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -10059,17 +9971,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MAN-TECH-11</t>
+          <t>V0-8.3</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Manifest › Shared Technical Contract</t>
+          <t>V0 §8</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Observability: structured logs, metrics, tracing and audit events</t>
+          <t>IP/device metadata where lawful</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -10079,10 +9991,10 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Medium - tracing spans, dashboards and SLOs are not part of V0 minimum</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
+          <t>Low — GDPR documentation gap.</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -10099,49 +10011,49 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Spans, dashboards and SLOs (see OBS-04, XP-12).</t>
+          <t>Document the lawful basis and retention period for IP address and user agent in the audit trail (the switch `AUDIT_CAPTURE_DEVICE_METADATA` exists and works); add to the privacy notice and the record of processing.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Logs, metrics, access logs and audit events are delivered; tracing spans are not.</t>
+          <t>The control exists; the legal determination and its documentation are the controller's and cannot be made by engineering.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Included in OBS-04 + dashboards (S)</t>
+          <t>S (1 d) + legal input</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>OBS-04</t>
+          <t>Retention policy decision (V0-S8)</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Tranche B (parallel with V1, before first production release)</t>
+          <t>Production gate (Tranche C, real AWS)</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Tranche B</t>
+          <t>Needs your / DPO decision</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>MAN-DOD-05</t>
+          <t>V0-S1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Manifest › Definition of Done</t>
+          <t>V0 Security</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>UI workflows are usable</t>
+          <t>Encryption in transit</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -10151,17 +10063,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>High — Definition of Done requires usable UI workflows; V0 foundations are API-only.</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
+          <t>Medium — unverified until deployed; internal hops unencrypted (acceptable for many baselines, not all).</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Decision needed</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -10171,49 +10083,49 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Build the V0 UI slices (members/invitations, documents with folders and visibility, tasks, workflows, notifications, AI proposals, audit log, feature flags) with axe checks. Option A (recommended): proceed with V1 API-first and deliver V0 slices in parallel under feature flags. Option B: hold V1 until the slices exist.</t>
+          <t>Verify TLS at the ALB, `rediss://`, `sslmode=require` and decide whether web-&gt;api traffic inside the VPC needs TLS.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>The Manifest's definition of done requires usable UI workflows. Everything V0 provides is reachable through the API only today (the UI covers authentication, security settings and companies).</t>
+          <t>Application-level controls (HSTS, secure cookies, config validation) are tested; infrastructure is not deployed.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>XL (3-4 w for documents, tasks, workflows, notifications, members, integrations, AI proposals, audit)</t>
+          <t>S (1-2 d)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>API is complete for all of them; design system</t>
+          <t>First apply</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Tranche B (parallel with V1, before first production release)</t>
+          <t>Production gate (Tranche C, real AWS)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Needs your decision (S5)</t>
+          <t>Production gate</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>MAN-DOD-08</t>
+          <t>V0-S2</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Manifest › Definition of Done</t>
+          <t>V0 Security</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Observability is present</t>
+          <t>Encrypted sensitive data at rest</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -10223,10 +10135,10 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>High — see OBS rows.</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
+          <t>Medium — application-level encryption verified; infrastructure encryption unverified. Field-key rotation procedure is documented, not implemented.</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -10243,49 +10155,49 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Closes with OBS-04 and OBS-05 (staging game-day).</t>
+          <t>Verify RDS, S3 and log encryption with the intended KMS keys; document field-key rotation.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Same as MAN-TECH-11.</t>
+          <t>Field-level encryption is tested; infrastructure encryption is only declared.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Included in OBS-04/OBS-05</t>
+          <t>S (1 d)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>OBS-04, OBS-05</t>
+          <t>First apply</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Tranche B (parallel with V1, before first production release)</t>
+          <t>Production gate (Tranche C, real AWS)</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Tranche B</t>
+          <t>Production gate</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>V0-6.1</t>
+          <t>V0-S4</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>V0 §6</t>
+          <t>V0 Security</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Upload</t>
+          <t>Least privilege</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -10295,10 +10207,10 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>High — see MAN-TECH-09; production ClamAV is not provisioned (REV-08).</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
+          <t>Low–Medium — IAM unreviewed in a real account.</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -10315,22 +10227,22 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Real-S3 run plus ClamAV service in AWS.</t>
+          <t>Review IAM in a real account; use separate database credentials for API and worker; enable `pgaudit`; add connection-level alerting. (Database-level least privilege - append-only privileges, role owns nothing - is tested.)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Upload pipeline verified against emulation and a real clamd only.</t>
+          <t>The database trusts the application to assert tenant and user for row-level security; arbitrary SQL execution as the runtime role would defeat it. No raw SQL from strings exists (architecture test).</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>S + REV-08</t>
+          <t>M (3 d)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>REV-08, MAN-TECH-09</t>
+          <t>First apply</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -10347,17 +10259,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>V0-6.10</t>
+          <t>V0-S6</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>V0 §6</t>
+          <t>V0 Security</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Immutable filing evidence</t>
+          <t>Secure object storage</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -10367,10 +10279,10 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Medium - application and database cannot alter locked evidence, but a privileged operator with bucket access could still delete the stored object until Object Lock is verified in AWS</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
+          <t>High — see MAN-TECH-09.</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -10387,22 +10299,22 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Verify S3 Object Lock in COMPLIANCE mode (the Terraform default is GOVERNANCE 30 days) for evidence versions; decide the retention default for locked evidence. The database already refuses every change to locked evidence.</t>
+          <t>See MAN-TECH-09.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Application and database immutability are proven; object-level immutability is not.</t>
+          <t>Same.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>S (1 d)</t>
+          <t>Included in MAN-TECH-09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>First Terraform apply</t>
+          <t>MAN-TECH-09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -10419,17 +10331,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>V0-7.1</t>
+          <t>V0-S7</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>V0 §7</t>
+          <t>V0 Security</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Backup and disaster recovery</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -10439,10 +10351,10 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Medium — deliverability/sandbox/DKIM/bounce handling untested; no bounce/complaint handling.</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
+          <t>High — documented ≠ recoverable. Documents (the evidence base) have versioning/Object Lock but no DR copy.</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -10459,22 +10371,22 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Exercise the SES adapter in staging (sandbox exit, DKIM, bounce/complaint handling with suppression).</t>
+          <t>Include S3 in AWS Backup / replication, back up Redis if queues must survive, drill a full restore.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Only file/memory drivers have been exercised.</t>
+          <t>RDS PITR and daily backups are configured; documents (the evidence base) have versioning and Object Lock but no DR copy.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>S (2 d)</t>
+          <t>M (3-4 d)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>SES domain/DKIM in the account</t>
+          <t>First apply</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -10491,17 +10403,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>V0-8.3</t>
+          <t>V0-S8</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>V0 §8</t>
+          <t>V0 Security</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>IP/device metadata where lawful</t>
+          <t>Retention policies</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -10511,17 +10423,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Low — GDPR documentation gap.</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
+          <t>Medium - unbounded growth of operational tables until the purge work (S4(b)) exists; UK GDPR storage-limitation needs the confirmed policy</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No (classification delivered)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -10531,49 +10443,49 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Document the lawful basis and retention period for IP address and user agent in the audit trail (the switch `AUDIT_CAPTURE_DEVICE_METADATA` exists and works); add to the privacy notice and the record of processing.</t>
+          <t>Scheduled purge jobs for operational tables (job_record, idempotency_record, expired sessions/tokens, notifications), a runtime-configurable policy and erasure-versus-retention rules, after the periods in the (delivered) classification are confirmed by the DPO/legal.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>The control exists; the legal determination and its documentation are the controller's and cannot be made by engineering.</t>
+          <t>The classification now exists, so V1 data is classified from its first row. Enforcement is needed before real client data is held in production; it depends on a decision engineering cannot make.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>S (1 d) + legal input</t>
+          <t>M-L (5 d)</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Retention policy decision (V0-S8)</t>
+          <t>DPO/legal decision on periods and lawful basis (V0-8.3); classification (S4(a)) is delivered</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Production gate (Tranche C, real AWS)</t>
+          <t>Tranche B (parallel with V1, before first production release) (before first production release)</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Needs your / DPO decision</t>
+          <t>Proposal S4(b) - not approved</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>V0-S1</t>
+          <t>XP-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>V0 Security</t>
+          <t>Cross-Platform §10</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Encryption in transit</t>
+          <t>Configurable data retention by category</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -10583,17 +10495,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Medium — unverified until deployed; internal hops unencrypted (acceptable for many baselines, not all).</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+          <t>Medium - classification exists, enforcement does not</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No (classification delivered)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -10603,49 +10515,49 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Verify TLS at the ALB, `rediss://`, `sslmode=require` and decide whether web-&gt;api traffic inside the VPC needs TLS.</t>
+          <t>Delivered together with V0-S8 (b): runtime-configurable retention by category and its enforcement.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Application-level controls (HSTS, secure cookies, config validation) are tested; infrastructure is not deployed.</t>
+          <t>Same requirement viewed from the cross-platform specification.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>S (1-2 d)</t>
+          <t>Included in V0-S8 (b)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>First apply</t>
+          <t>V0-S8</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Production gate (Tranche C, real AWS)</t>
+          <t>Tranche B (parallel with V1, before first production release)</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Production gate</t>
+          <t>Proposal S4(b) - not approved</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>V0-S2</t>
+          <t>XP-11</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>V0 Security</t>
+          <t>Cross-Platform §11</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Encrypted sensitive data at rest</t>
+          <t>Accessibility (WCAG-aligned, keyboard, contrast)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -10655,10 +10567,10 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Medium — application-level encryption verified; infrastructure encryption unverified. Field-key rotation procedure is documented, not implemented.</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
+          <t>Medium — unverified compliance; legal exposure for public-facing client portal later.</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -10675,49 +10587,49 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Verify RDS, S3 and log encryption with the intended KMS keys; document field-key rotation.</t>
+          <t>Add automated accessibility checks (axe) to the e2e suite for every UI slice; keyboard and contrast review.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Field-level encryption is tested; infrastructure encryption is only declared.</t>
+          <t>Cannot be verified without the UI; legal exposure grows with the client portal (V7).</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>S (1 d)</t>
+          <t>M (with the UI slices)</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>First apply</t>
+          <t>MAN-DOD-05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Production gate (Tranche C, real AWS)</t>
+          <t>Tranche B (parallel with V1, before first production release)</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Production gate</t>
+          <t>With S5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>V0-S4</t>
+          <t>XP-12</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>V0 Security</t>
+          <t>Cross-Platform §12</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Least privilege</t>
+          <t>Heavy operations async with visible progress</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -10727,10 +10639,10 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Low–Medium — IAM unreviewed in a real account.</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
+          <t>Medium — 'feels immediate' is untested.</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -10747,62 +10659,62 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Review IAM in a real account; use separate database credentials for API and worker; enable `pgaudit`; add connection-level alerting. (Database-level least privilege - append-only privileges, role owns nothing - is tested.)</t>
+          <t>Define SLOs, add k6 smoke/load tests for the heavy paths (upload, import/export, report), expose job progress in the UI.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>The database trusts the application to assert tenant and user for row-level security; arbitrary SQL execution as the runtime role would defeat it. No raw SQL from strings exists (architecture test).</t>
+          <t>'Feels immediate' is untested; async behaviour and progress are implemented and tested.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>M (3 d)</t>
+          <t>M (4 d)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>First apply</t>
+          <t>Staging environment, SLO definitions</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Production gate (Tranche C, real AWS)</t>
+          <t>Tranche B (parallel with V1, before first production release)</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Production gate</t>
+          <t>Tranche B (already planned)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>V0-S6</t>
+          <t>OBS-04</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>V0 Security</t>
+          <t>Manifest › Observability</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Secure object storage</t>
+          <t>Distributed tracing</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>High — see MAN-TECH-09.</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -10819,49 +10731,49 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>See MAN-TECH-09.</t>
+          <t>OpenTelemetry SDK + ADOT collector replacing the metrics renderers' transport; spans for HTTP, database, queue and job execution. Trace-id propagation API -&gt; job -&gt; worker already exists.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Same.</t>
+          <t>Correlation ids, trace ids, access logs and metrics cover incident triage; spans add latency breakdown.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Included in MAN-TECH-09</t>
+          <t>M (4 d)</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>MAN-TECH-09</t>
+          <t>ADOT collector in ECS (Terraform)</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Production gate (Tranche C, real AWS)</t>
+          <t>Tranche B (parallel with V1, before first production release)</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Production gate</t>
+          <t>Tranche B (already planned)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>V0-S7</t>
+          <t>OBS-05</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>V0 Security</t>
+          <t>Manifest › Observability</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Backup and disaster recovery</t>
+          <t>Alerting on DLQ, failed outbox, auth attacks, readiness</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -10871,10 +10783,10 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>High — documented ≠ recoverable. Documents (the evidence base) have versioning/Object Lock but no DR copy.</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
+          <t>Medium - defined and validated, but never applied: delivery of alarms to a real inbox and EMF extraction are unproven</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -10891,22 +10803,22 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Include S3 in AWS Backup / replication, back up Redis if queues must survive, drill a full restore.</t>
+          <t>Apply the alarms in staging, confirm EMF extraction and e-mail delivery, run a game-day (stop the worker, fill the DLQ, fail an outbox event).</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>RDS PITR and daily backups are configured; documents (the evidence base) have versioning and Object Lock but no DR copy.</t>
+          <t>Alarms are defined and validated by terraform validate and a drift-guard test but have never run in a real account.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>M (3-4 d)</t>
+          <t>S (2 d) in staging</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>First apply</t>
+          <t>First Terraform apply (REV-05)</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10923,30 +10835,30 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>XP-11</t>
+          <t>REV-04</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Cross-Platform §11</t>
+          <t>Review request #3</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Accessibility (WCAG-aligned, keyboard, contrast)</t>
+          <t>Moto-based S3 vs real AWS S3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Medium — unverified compliance; legal exposure for public-facing client portal later.</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
+          <t>High — real-S3 validation has never been performed.</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -10963,49 +10875,49 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Add automated accessibility checks (axe) to the e2e suite for every UI slice; keyboard and contrast review.</t>
+          <t>Same run as MAN-TECH-09.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Cannot be verified without the UI; legal exposure grows with the client portal (V7).</t>
+          <t>Signature enforcement, expiry and KMS are not validated by moto.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>M (with the UI slices)</t>
+          <t>S (2 d)</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>MAN-DOD-05</t>
+          <t>Staging AWS account</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Tranche B (parallel with V1, before first production release)</t>
+          <t>Production gate (Tranche C, real AWS)</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>With S5</t>
+          <t>Production gate</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>XP-12</t>
+          <t>REV-05</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Cross-Platform §12</t>
+          <t>Review request #4</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Heavy operations async with visible progress</t>
+          <t>Terraform validation vs AWS deployment</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -11015,10 +10927,10 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Medium — 'feels immediate' is untested.</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
+          <t>High — plan/apply failures (quotas, IAM, KMS policy, name collisions, SES) are likely on first apply.</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -11035,62 +10947,62 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Define SLOs, add k6 smoke/load tests for the heavy paths (upload, import/export, report), expose job progress in the UI.</t>
+          <t>`terraform plan`/`apply` in staging, fix first-apply failures (quotas, IAM, KMS policy, names, SES), destroy/recreate once. CI proves only fmt/init/validate.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>'Feels immediate' is untested; async behaviour and progress are implemented and tested.</t>
+          <t>Validation checks syntax, types and references only.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>M (4 d)</t>
+          <t>M (3-4 d)</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Staging environment, SLO definitions</t>
+          <t>AWS account, state backend</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Tranche B (parallel with V1, before first production release)</t>
+          <t>Production gate (Tranche C, real AWS)</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Tranche B (already planned)</t>
+          <t>Production gate</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>OBS-04</t>
+          <t>REV-07</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Manifest › Observability</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Distributed tracing</t>
+          <t>Web ↔ API deployment configuration</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
+          <t>Medium — staging/other envs need a rebuilt image or will call prod's DNS name.</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -11107,62 +11019,62 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>OpenTelemetry SDK + ADOT collector replacing the metrics renderers' transport; spans for HTTP, database, queue and job execution. Trace-id propagation API -&gt; job -&gt; worker already exists.</t>
+          <t>Resolve the API URL at runtime (or build per environment) instead of baking `API_INTERNAL_URL` into the web image.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Correlation ids, trace ids, access logs and metrics cover incident triage; spans add latency breakdown.</t>
+          <t>Other environments would call the production DNS name.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>M (4 d)</t>
+          <t>S (1 d)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>ADOT collector in ECS (Terraform)</t>
+          <t>Web build</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Tranche B (parallel with V1, before first production release)</t>
+          <t>Production gate (Tranche C, real AWS)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Tranche B (already planned)</t>
+          <t>Production gate</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>OBS-05</t>
+          <t>REV-08</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Manifest › Observability</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Alerting on DLQ, failed outbox, auth attacks, readiness</t>
+          <t>ClamAV in AWS</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Medium - defined and validated, but never applied: delivery of alarms to a real inbox and EMF extraction are unproven</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
+          <t>High — in production every upload would fail scanning and stay in SCANNING (fails closed, but the feature is unusable).</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -11174,27 +11086,27 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (hard blocker)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Apply the alarms in staging, confirm EMF extraction and e-mail delivery, run a game-day (stop the worker, fill the DLQ, fail an outbox event).</t>
+          <t>Provision ClamAV (ECS service with the official image, private service discovery name, `CLAMAV_HOST` for api and worker, signature-update egress).</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Alarms are defined and validated by terraform validate and a drift-guard test but have never run in a real account.</t>
+          <t>Production configuration demands the clamav driver, but nothing in Terraform provisions it: every upload would stay SCANNING (fails closed).</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>S (2 d) in staging</t>
+          <t>M (3 d)</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>First Terraform apply (REV-05)</t>
+          <t>Terraform: ECS service + service discovery for clamd</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -11211,17 +11123,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>REV-04</t>
+          <t>REV-09</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Review request #3</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Moto-based S3 vs real AWS S3</t>
+          <t>Redis configuration for BullMQ</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -11231,10 +11143,10 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>High — real-S3 validation has never been performed.</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -11251,22 +11163,22 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Same run as MAN-TECH-09.</t>
+          <t>Replace `default.redis7` with a parameter group setting `maxmemory-policy noeviction` (required by BullMQ) and add the Redis eviction alarm.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Signature enforcement, expiry and KMS are not validated by moto.</t>
+          <t>Default eviction can drop queued jobs under memory pressure.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>S (2 d)</t>
+          <t>S (0.5 d)</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Staging AWS account</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -11283,17 +11195,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>REV-05</t>
+          <t>REV-10</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Review request #4</t>
+          <t>Review request #6</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Terraform validation vs AWS deployment</t>
+          <t>Migrations and recovery documentation</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -11303,10 +11215,10 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>High — plan/apply failures (quotas, IAM, KMS policy, name collisions, SES) are likely on first apply.</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -11323,22 +11235,22 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>`terraform plan`/`apply` in staging, fix first-apply failures (quotas, IAM, KMS policy, names, SES), destroy/recreate once. CI proves only fmt/init/validate.</t>
+          <t>Rehearse a failed migration and a restore from the latest snapshot in staging; record timings in the runbook.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Validation checks syntax, types and references only.</t>
+          <t>Procedures are documented and the migration path is tested from scratch and on populated databases, but no restore has been drilled.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>M (3-4 d)</t>
+          <t>S (2 d)</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>AWS account, state backend</t>
+          <t>Staging DB snapshot</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -11355,7 +11267,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>REV-07</t>
+          <t>REV-11</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -11365,7 +11277,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Web ↔ API deployment configuration</t>
+          <t>Database connection management</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -11375,10 +11287,10 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Medium — staging/other envs need a rebuilt image or will call prod's DNS name.</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -11395,62 +11307,62 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Resolve the API URL at runtime (or build per environment) instead of baking `API_INTERNAL_URL` into the web image.</t>
+          <t>Set explicit pool sizes per service, consider RDS Proxy, size `rds_connections` alarm from measurement.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Other environments would call the production DNS name.</t>
+          <t>Default pool sizes times api and worker tasks could exhaust connections under load.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>S (1 d)</t>
+          <t>S-M (2-3 d)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Web build</t>
+          <t>Load test (XP-12)</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Production gate (Tranche C, real AWS)</t>
+          <t>Tranche B (parallel with V1, before first production release)</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Production gate</t>
+          <t>Tranche B</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>REV-08</t>
+          <t>REV-13</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>V6 §Human-in-the-Loop / Explainability / Privacy (forward)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ClamAV in AWS</t>
+          <t>AI state vocabulary (V6: SUGGESTED -&gt; REVIEWED -&gt; ACCEPTED/REJECTED), explainability (prompt version, evidence, confidence) and privacy gate</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>High — in production every upload would fail scanning and stay in SCANNING (fails closed, but the feature is unusable).</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
+          <t>Medium - privacy gate missing (low until real providers are enabled)</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>MUST FIX BEFORE PRODUCTION</t>
         </is>
@@ -11462,69 +11374,69 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Yes (hard blocker)</t>
+          <t>Yes (before any external AI provider)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Provision ClamAV (ECS service with the official image, private service discovery name, `CLAMAV_HOST` for api and worker, signature-update egress).</t>
+          <t>Per-organisation AI data-processing consent record (who accepted what, when) checked before any external provider call. Today AI and OCR are off by default per organisation (`ai.beta`, `documents.ocr`) and no external provider exists.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Production configuration demands the clamav driver, but nothing in Terraform provisions it: every upload would stay SCANNING (fails closed).</t>
+          <t>Privacy gate for external AI; not needed while only fake providers exist.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>M (3 d)</t>
+          <t>S (2 d)</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Terraform: ECS service + service discovery for clamd</t>
+          <t>Legal input on data processing</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Production gate (Tranche C, real AWS)</t>
+          <t>Tranche B (parallel with V1, before first production release)</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Production gate</t>
+          <t>Needs your decision</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>REV-09</t>
+          <t>V0-1.9</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>V0 §1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Redis configuration for BullMQ</t>
+          <t>device/session management</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Medium — spec asks for device management; security teams expect new-device notification and admin kill-switch.</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>MUST FIX BEFORE PRODUCTION</t>
+          <t>DEFER TO A LATER VERSION</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11534,54 +11446,54 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Recommended (new-device alert)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Replace `default.redis7` with a parameter group setting `maxmemory-policy noeviction` (required by BullMQ) and add the Redis eviction alarm.</t>
+          <t>Add a stable device identity (cookie-bound), new-device e-mail alert, per-device revoke and an admin 'revoke all sessions for a user' kill-switch. Sessions are already listed and revocable, MFA exists, sessions are server-side and revoked on password reset.</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Default eviction can drop queued jobs under memory pressure.</t>
+          <t>Hardening, not a V1 dependency. Becomes important when external client users arrive (V7). Recommended before production for staff accounts.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>S (0.5 d)</t>
+          <t>M (4 d)</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Notification channel port (V0-7.3) for the new-device alert</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Production gate (Tranche C, real AWS)</t>
+          <t>Tranche B (parallel with V1, before first production release) / V7 client portal</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Production gate</t>
+          <t>Proposal S3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>REV-10</t>
+          <t>V0-9.2</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Review request #6</t>
+          <t>V0 §9</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Migrations and recovery documentation</t>
+          <t>Adapters for HMRC, Companies House, banks, Xero, QuickBooks, FreeAgent, Stripe, Shopify, payroll, payment providers</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -11591,12 +11503,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low — appropriate for V0 'foundation'.</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>MUST FIX BEFORE PRODUCTION</t>
+          <t>DEFER TO A LATER VERSION</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11606,69 +11518,69 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Rehearse a failed migration and a restore from the latest snapshot in staging; record timings in the runbook.</t>
+          <t>Named adapters are delivered by the versions that need them, through the existing adapter interface and registry (the only place providers are registered). The V0 deliverable - the interface, credential encryption, host allow-list, mock adapter, retries - is complete.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Procedures are documented and the migration path is tested from scratch and on populated databases, but no restore has been drilled.</t>
+          <t>The V0 specification asks for an 'adapter interface'; the named providers are the work of later versions.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>S (2 d)</t>
+          <t>n/a for V0</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Staging DB snapshot</t>
+          <t>V3 / V4 / V5 / V11</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Production gate (Tranche C, real AWS)</t>
+          <t>V3 (Companies House), V4/V5 (HMRC), V11 (banks, Xero, QuickBooks, FreeAgent, Stripe, Shopify, payroll)</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Production gate</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>REV-11</t>
+          <t>V0-10.3</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>V0 §10</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Database connection management</t>
+          <t>Embedding/Search provider</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Medium — universal search/AI retrieval (Cross-Platform §2, V10).</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>MUST FIX BEFORE PRODUCTION</t>
+          <t>DEFER TO A LATER VERSION</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11678,139 +11590,139 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Set explicit pool sizes per service, consider RDS Proxy, size `rds_connections` alarm from measurement.</t>
+          <t>Add EmbeddingProvider and SearchProvider ports with deterministic fakes (no storage, no endpoints), beside the existing AI and OCR ports.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Default pool sizes times api and worker tasks could exhaust connections under load.</t>
+          <t>Pure abstraction with no V1 consumer; first needed by V6/V10 (universal search, retrieval). Doing it now is cheap and would let V0 §10 be marked complete.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>S-M (2-3 d)</t>
+          <t>S (1-2 d) if done now</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Load test (XP-12)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Tranche B (parallel with V1, before first production release)</t>
+          <t>V6 (OCR/AI) - or the Pre-V1 gate if you want V0 spec-complete</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Tranche B</t>
+          <t>Proposal S7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>REV-13</t>
+          <t>XP-02</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>V6 §Human-in-the-Loop / Explainability / Privacy (forward)</t>
+          <t>Cross-Platform §2</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>AI state vocabulary (V6: SUGGESTED -&gt; REVIEWED -&gt; ACCEPTED/REJECTED), explainability (prompt version, evidence, confidence) and privacy gate</t>
+          <t>Universal search</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Medium - privacy gate missing (low until real providers are enabled)</t>
+          <t>Medium (design) — search technology (Postgres FTS vs OpenSearch) and per-tenant index design should be decided before V1 data models.</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>MUST FIX BEFORE PRODUCTION</t>
+          <t>DEFER TO A LATER VERSION</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>Design decision</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Yes (before any external AI provider)</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Per-organisation AI data-processing consent record (who accepted what, when) checked before any external provider call. Today AI and OCR are off by default per organisation (`ai.beta`, `documents.ocr`) and no external provider exists.</t>
+          <t>Decide search technology (Postgres FTS vs OpenSearch) and per-tenant index design before V1 reporting.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Privacy gate for external AI; not needed while only fake providers exist.</t>
+          <t>Design decision, no V0 code.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>S (2 d)</t>
+          <t>M design</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Legal input on data processing</t>
+          <t>Document extraction (delivered)</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Tranche B (parallel with V1, before first production release)</t>
+          <t>V1 design / V10</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Needs your decision</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>V0-1.9</t>
+          <t>XP-03</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>V0 §1</t>
+          <t>Cross-Platform §3–5</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>device/session management</t>
+          <t>Exception-first UX, command centre, materiality engine</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Medium — spec asks for device management; security teams expect new-device notification and admin kill-switch.</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
+          <t>Low — materiality settings store should be designed with company profile (R1).</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>DEFER TO A LATER VERSION</t>
         </is>
@@ -11822,54 +11734,54 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Recommended (new-device alert)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Add a stable device identity (cookie-bound), new-device e-mail alert, per-device revoke and an admin 'revoke all sessions for a user' kill-switch. Sessions are already listed and revocable, MFA exists, sessions are server-side and revoked on password reset.</t>
+          <t>Materiality settings store designed with the company profile in V1/V2.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Hardening, not a V1 dependency. Becomes important when external client users arrive (V7). Recommended before production for staff accounts.</t>
+          <t>Product features of later versions.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>M (4 d)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Notification channel port (V0-7.3) for the new-device alert</t>
+          <t>V1+</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Tranche B (parallel with V1, before first production release) / V7 client portal</t>
+          <t>V1+</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Proposal S3</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>V0-9.2</t>
+          <t>REV-12</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>V0 §9</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Adapters for HMRC, Companies House, banks, Xero, QuickBooks, FreeAgent, Stripe, Shopify, payroll, payment providers</t>
+          <t>Container images</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -11879,10 +11791,10 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Low — appropriate for V0 'foundation'.</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
+          <t>Low–Medium — larger attack surface/size.</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>DEFER TO A LATER VERSION</t>
         </is>
@@ -11899,27 +11811,27 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Named adapters are delivered by the versions that need them, through the existing adapter interface and registry (the only place providers are registered). The V0 deliverable - the interface, credential encryption, host allow-list, mock adapter, retries - is complete.</t>
+          <t>Multi-stage prune of dev dependencies and sources from runtime images (`pnpm deploy`). The Trivy HIGH/CRITICAL gate, OS upgrade and npm removal are done.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>The V0 specification asks for an 'adapter interface'; the named providers are the work of later versions.</t>
+          <t>Size and surface reduction; the scan gate is passing on all four images.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>n/a for V0</t>
+          <t>S (1-2 d)</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>V3 / V4 / V5 / V11</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>V3 (Companies House), V4/V5 (HMRC), V11 (banks, Xero, QuickBooks, FreeAgent, Stripe, Shopify, payroll)</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11931,30 +11843,30 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>V0-10.3</t>
+          <t>CHG-DEF1</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>V0 §10</t>
+          <t>Deliberately not built (scope)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Embedding/Search provider</t>
+          <t>Cross-organisation engagement (a client business with its own organisation instructing a practice), billing/seat counting, UI for practices and grants, audit/job/integration company dimension</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Medium — universal search/AI retrieval (Cross-Platform §2, V10).</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
+          <t>Medium - needed before client-portal/billing work</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>DEFER TO A LATER VERSION</t>
         </is>
@@ -11971,49 +11883,49 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Add EmbeddingProvider and SearchProvider ports with deterministic fakes (no storage, no endpoints), beside the existing AI and OCR ports.</t>
+          <t>Explicit cross-organisation engagement grant when a client business needs its own organisation.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Pure abstraction with no V1 consumer; first needed by V6/V10 (universal search, retrieval). Doing it now is cheap and would let V0 §10 be marked complete.</t>
+          <t>Deliberately not built (documented in the design).</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>S (1-2 d) if done now</t>
+          <t>M-L</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
+          <t>Hierarchy design section 8</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>V7 (client portal / billing)</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
           <t>None</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>V6 (OCR/AI) - or the Pre-V1 gate if you want V0 spec-complete</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>Proposal S7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>XP-02</t>
+          <t>MAN-CTRL-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Cross-Platform §2</t>
+          <t>Manifest › Non-Negotiable Accounting Controls 1–9</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Universal search</t>
+          <t>PostingService, immutable posted journals, reversals, balanced entries, source/actor/timestamp metadata, traceability, drill-down, period states, effective-dated rules</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -12023,17 +11935,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Medium (design) — search technology (Postgres FTS vs OpenSearch) and per-tenant index design should be decided before V1 data models.</t>
+          <t>None for V0. Pre-V1 design risk: a dedicated posting DB role + trigger pattern (like forbid_mutation) must be designed before V1 coding.</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>DEFER TO A LATER VERSION</t>
+          <t>NOT APPLICABLE (justified)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Design decision</t>
+          <t>Design input</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -12043,27 +11955,27 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Decide search technology (Postgres FTS vs OpenSearch) and per-tenant index design before V1 reporting.</t>
+          <t>Accounting controls are V1 deliverables; V0 supplies the primitives (append-only pattern, central authoriser, outbox).</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Design decision, no V0 code.</t>
+          <t>Not a V0 requirement.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>M design</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Document extraction (delivered)</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>V1 design / V10</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12075,17 +11987,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>XP-03</t>
+          <t>MAN-DIFF</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Cross-Platform §3–5</t>
+          <t>Manifest › Strategic Differentiators</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Exception-first UX, command centre, materiality engine</t>
+          <t>AI bookkeeping, working papers, CFO forecasting, etc.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -12095,12 +12007,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Low — materiality settings store should be designed with company profile (R1).</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>DEFER TO A LATER VERSION</t>
+          <t>NOT APPLICABLE (justified)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12115,12 +12027,12 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Materiality settings store designed with the company profile in V1/V2.</t>
+          <t>Differentiators are later versions.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Product features of later versions.</t>
+          <t>Not a V0 requirement.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -12130,12 +12042,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>V1+</t>
+          <t>V6-V12</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>V1+</t>
+          <t>V6-V12</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12147,17 +12059,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>REV-12</t>
+          <t>V0-1.5</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>V0 §1 + Core Tables</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Container images</t>
+          <t>permissions (entity/table)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -12167,12 +12079,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Low–Medium — larger attack surface/size.</t>
+          <t>Low — functionally complete; a table would only help dynamic permission registration by V8–V12 plug-ins.</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>DEFER TO A LATER VERSION</t>
+          <t>NOT APPLICABLE (justified)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12187,17 +12099,17 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Multi-stage prune of dev dependencies and sources from runtime images (`pnpm deploy`). The Trivy HIGH/CRITICAL gate, OS upgrade and npm removal are done.</t>
+          <t>Accept the deviation: the permission catalogue lives in code (typed, test-synchronised with the database role seed) and `role.permissions` stores grants. A `permissions` table would create a second source of truth.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Size and surface reduction; the scan gate is passing on all four images.</t>
+          <t>Functionally complete and tested (permission matrix: 8 roles x 32 probes); only dynamic plug-in registration (V8-V12) would benefit.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>S (1-2 d)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -12207,29 +12119,29 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Needs your acceptance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>CHG-DEF1</t>
+          <t>V0-T2</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Deliberately not built (scope)</t>
+          <t>V0 Core Tables</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Cross-organisation engagement (a client business with its own organisation instructing a practice), billing/seat counting, UI for practices and grants, audit/job/integration company dimension</t>
+          <t>permissions, contacts, integration_jobs, ai_requests</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -12239,12 +12151,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Medium - needed before client-portal/billing work</t>
+          <t>See linked rows</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>DEFER TO A LATER VERSION</t>
+          <t>NOT APPLICABLE (justified)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12259,49 +12171,49 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Explicit cross-organisation engagement grant when a client business needs its own organisation.</t>
+          <t>Accept the deviations: `contacts` now exists; `permissions` is the code catalogue (see V0-1.5); `integration_jobs` is `job_record` (queue `integrations`, with company and trace ids); `ai_requests` is `ai_run`.</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Deliberately not built (documented in the design).</t>
+          <t>Equivalent function, singular snake_case naming approved under D5.</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>M-L</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Hierarchy design section 8</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>V7 (client portal / billing)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Needs your acceptance</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MAN-CTRL-01</t>
+          <t>XP-01</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Manifest › Non-Negotiable Accounting Controls 1–9</t>
+          <t>Cross-Platform §1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>PostingService, immutable posted journals, reversals, balanced entries, source/actor/timestamp metadata, traceability, drill-down, period states, effective-dated rules</t>
+          <t>Universal drill-down</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -12311,17 +12223,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>None for V0. Pre-V1 design risk: a dedicated posting DB role + trigger pattern (like forbid_mutation) must be designed before V1 coding.</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
+          <t>None for V0 (see XP-06 for the foundation)</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>NOT APPLICABLE (justified)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Design input</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -12331,12 +12243,12 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Accounting controls are V1 deliverables; V0 supplies the primitives (append-only pattern, central authoriser, outbox).</t>
+          <t>The evidence graph (XP-06, delivered) is the V0 foundation for drill-down.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Not a V0 requirement.</t>
+          <t>UI/report feature of later versions.</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -12346,12 +12258,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>V1+</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>V1+</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -12363,17 +12275,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MAN-DIFF</t>
+          <t>XP-13</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Manifest › Strategic Differentiators</t>
+          <t>Cross-Platform §13–14</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>AI bookkeeping, working papers, CFO forecasting, etc.</t>
+          <t>Mobile-first portal; product design language</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -12383,345 +12295,57 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>None for V0</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE (justified)</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Mobile-first portal is V7.</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Not a V0 requirement.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>NOT APPLICABLE (justified)</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Differentiators are later versions.</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Not a V0 requirement.</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>V6-V12</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>V6-V12</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>V0-1.5</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>V0 §1 + Core Tables</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>permissions (entity/table)</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Low — functionally complete; a table would only help dynamic permission registration by V8–V12 plug-ins.</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>NOT APPLICABLE (justified)</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Accept the deviation: the permission catalogue lives in code (typed, test-synchronised with the database role seed) and `role.permissions` stores grants. A `permissions` table would create a second source of truth.</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Functionally complete and tested (permission matrix: 8 roles x 32 probes); only dynamic plug-in registration (V8-V12) would benefit.</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>Needs your acceptance</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>V0-T2</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>V0 Core Tables</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>permissions, contacts, integration_jobs, ai_requests</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>See linked rows</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>NOT APPLICABLE (justified)</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Accept the deviations: `contacts` now exists; `permissions` is the code catalogue (see V0-1.5); `integration_jobs` is `job_record` (queue `integrations`, with company and trace ids); `ai_requests` is `ai_run`.</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>Equivalent function, singular snake_case naming approved under D5.</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>Needs your acceptance</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>XP-01</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Cross-Platform §1</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Universal drill-down</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>NOT APPLICABLE</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>None for V0 (see XP-06 for the foundation)</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>NOT APPLICABLE (justified)</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>The evidence graph (XP-06, delivered) is the V0 foundation for drill-down.</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>UI/report feature of later versions.</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>V1+</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>V1+</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>XP-13</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Cross-Platform §13–14</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Mobile-first portal; product design language</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>NOT APPLICABLE</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>None for V0</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>NOT APPLICABLE (justified)</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Mobile-first portal is V7.</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Not a V0 requirement.</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>V7</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>V7</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N45"/>
+  <autoFilter ref="A1:N41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12787,12 +12411,12 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Before V1</t>
+          <t>DELIVERED (approved)</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Additive; migration + sweeper reusing the task-reminder pattern</t>
+          <t>Migration 20260105000000, ADR-37, tests/platform/workflow-overdue.test.ts, tests/api/workflow-deadlines.test.ts</t>
         </is>
       </c>
     </row>
@@ -12814,12 +12438,12 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Before V1</t>
+          <t>DELIVERED (approved)</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Refactors NotificationService behind a port; five call sites</t>
+          <t>Migration 20260105000100, ADR-38, tests/platform/notification-channels.test.ts, tests/api/notification-preferences.test.ts</t>
         </is>
       </c>
     </row>
@@ -12868,12 +12492,12 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>(a) before V1, (b) before production</t>
+          <t>(a) DELIVERED (approved); (b) before production, NOT approved</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Needs your decision on retention periods and the lawful basis (V0-8.3)</t>
+          <t>(a) migration 20260105000200, ADR-39, tests/db/retention.test.ts. (b) needs your decision on retention periods and the lawful basis (V0-8.3)</t>
         </is>
       </c>
     </row>
@@ -12922,12 +12546,12 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Before V1</t>
+          <t>DELIVERED (approved)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Test infrastructure only</t>
+          <t>ADR-36, tests/jobs/integration-retry.test.ts</t>
         </is>
       </c>
     </row>

--- a/docs/architecture/v0-compliance-matrix.xlsx
+++ b/docs/architecture/v0-compliance-matrix.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High-risk findings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision register" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope proposals" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product owner decisions" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matrix'!$A$1:$N$145</definedName>
@@ -9676,7 +9677,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Needs your decision (S5)</t>
+          <t>APPROVED approach 2026-10-09 (DEC-002, ADR-40): API-first V1, V0 screens in parallel behind feature flags. Row stays open until the screens exist</t>
         </is>
       </c>
     </row>
@@ -10036,7 +10037,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Needs your / DPO decision</t>
+          <t>DEFERRED FOR APPROVAL 2026-10-09 (DEC-003, ADR-41): flagged in docs/legal/retention-verification-schedule.md section 2</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10469,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Proposal S4(b) - not approved</t>
+          <t>S4(b) FROZEN 2026-10-09 (DEC-003, ADR-41): no purge/erasure/enforcement until the schedule and lawful basis are approved; periods stay PROVISIONAL</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10541,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Proposal S4(b) - not approved</t>
+          <t>S4(b) FROZEN 2026-10-09 (DEC-003, ADR-41)</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10613,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>With S5</t>
+          <t>Follows DEC-002 (ADR-40)</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11477,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Proposal S3</t>
+          <t>DEFERRED to a later tranche 2026-10-09 (DEC-005, ADR-43)</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11621,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Proposal S7</t>
+          <t>DEFERRED to a later tranche 2026-10-09 (DEC-005, ADR-43)</t>
         </is>
       </c>
     </row>
@@ -12124,7 +12125,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Needs your acceptance</t>
+          <t>ACCEPTED by the product owner 2026-10-09 (DEC-004, ADR-42)</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12197,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Needs your acceptance</t>
+          <t>ACCEPTED by the product owner 2026-10-09 (DEC-004, ADR-42)</t>
         </is>
       </c>
     </row>
@@ -12585,4 +12586,200 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="120" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>DEC-001</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>V0 readiness</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED to start V1 on the basis of this report. The pre-V1 bundle S1, S2, S4(a), S6 is accepted as complete. NOT production approval: no production deployment or live-customer processing on this basis alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>DEC-002</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>UI strategy (S5; MAN-DOD-05, XP-11)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED: API-first V1; V0 UI screens in parallel behind feature flags; prioritise end-to-end bookkeeping workflows; UI tested against the real API, authorisation and tenant boundaries. Rows stay open until the screens exist and pass accessibility checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>DEC-003</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Retention and privacy (V0-S8, XP-10, V0-8.3; S4(b))</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>DEFERRED FOR APPROVAL: all periods stay PROVISIONAL; S4(b) frozen; legal verification schedule prepared (docs/legal/retention-verification-schedule.md and .xlsx, UNVERIFIED); IP address and user agent flagged for privacy review; synthetic/test data only until decided. Rows stay PARTIALLY IMPLEMENTED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>DEC-004</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Naming deviations (V0-1.5, V0-T2)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPTED as documented, including job_record as the integration job table (ADR-36); conditions for separating the models in ADR-42. Row statuses are NOT changed by this acceptance (they remain PARTIALLY IMPLEMENTED with the deviation accepted).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>DEC-005</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>S3 device identity (V0-1.9) and S7 embedding/search ports (V0-10.3)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>DEFERRED to later tranches; baseline authentication, session revocation, authorisation and tenant isolation must not be weakened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>DEC-006</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>NOT approved. AWS deployment and production hardening remain explicit gates; Terraform validate in CI is not evidence of an applied or verified infrastructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>DEC-007</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>V1 conduct</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>V1 follows the approved order and manifest; no scope expansion into deferred items without a recorded decision; each V1 milestone is accepted with commit SHA, CI run, test results, migrations, security/permission checks, matrix changes and known limitations; this matrix and report stay as versioned evidence (git history is the audit trail).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>